--- a/research/traditional_assets/database/data/tunisia/tunisia_retail_general.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_retail_general.xlsx
@@ -1257,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1394,22 +1394,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2028636545692241</v>
+        <v>0.2025976090873702</v>
       </c>
       <c r="C2">
-        <v>28.3</v>
+        <v>28.04585695455307</v>
       </c>
       <c r="D2">
-        <v>28.3</v>
+        <v>28.32885695455307</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1430,28 +1430,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0142349</v>
       </c>
       <c r="N2">
-        <v>2.139999999999999</v>
+        <v>2.125765099999999</v>
       </c>
       <c r="O2">
-        <v>0.3209999999999998</v>
+        <v>0.3188647649999998</v>
       </c>
       <c r="P2">
-        <v>1.818999999999999</v>
+        <v>1.806900334999999</v>
       </c>
       <c r="Q2">
-        <v>10.779</v>
+        <v>10.766900335</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2028636545692241</v>
+        <v>0.2042121808963336</v>
       </c>
       <c r="T2">
-        <v>0.960581759320096</v>
+        <v>0.9688291784657735</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>150.3347406725723</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1476,22 +1476,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2025976090873702</v>
+        <v>0.2023315636055164</v>
       </c>
       <c r="C3">
-        <v>28.04585695455307</v>
+        <v>27.79177281891568</v>
       </c>
       <c r="D3">
-        <v>28.32885695455307</v>
+        <v>28.35777281891568</v>
       </c>
       <c r="E3">
-        <v>0.283</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="F3">
-        <v>0.283</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1512,28 +1512,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M3">
-        <v>0.0142349</v>
+        <v>0.0284698</v>
       </c>
       <c r="N3">
-        <v>2.125765099999999</v>
+        <v>2.111530199999999</v>
       </c>
       <c r="O3">
-        <v>0.3188647649999998</v>
+        <v>0.3167295299999998</v>
       </c>
       <c r="P3">
-        <v>1.806900334999999</v>
+        <v>1.794800669999999</v>
       </c>
       <c r="Q3">
-        <v>10.766900335</v>
+        <v>10.75480067</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2042121808963336</v>
+        <v>0.2055882281688943</v>
       </c>
       <c r="T3">
-        <v>0.9688291784657735</v>
+        <v>0.9772449122878937</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.3347406725723</v>
+        <v>75.16737033628613</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1558,22 +1558,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2023315636055164</v>
+        <v>0.2020655181236626</v>
       </c>
       <c r="C4">
-        <v>27.79177281891568</v>
+        <v>27.53774777366362</v>
       </c>
       <c r="D4">
-        <v>28.35777281891568</v>
+        <v>28.38674777366362</v>
       </c>
       <c r="E4">
-        <v>0.5660000000000001</v>
+        <v>0.849</v>
       </c>
       <c r="F4">
-        <v>0.5660000000000001</v>
+        <v>0.849</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1594,28 +1594,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M4">
-        <v>0.0284698</v>
+        <v>0.0427047</v>
       </c>
       <c r="N4">
-        <v>2.111530199999999</v>
+        <v>2.097295299999999</v>
       </c>
       <c r="O4">
-        <v>0.3167295299999998</v>
+        <v>0.3145942949999999</v>
       </c>
       <c r="P4">
-        <v>1.794800669999999</v>
+        <v>1.782701004999999</v>
       </c>
       <c r="Q4">
-        <v>10.75480067</v>
+        <v>10.742701005</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2055882281688943</v>
+        <v>0.2069926475501676</v>
       </c>
       <c r="T4">
-        <v>0.9772449122878937</v>
+        <v>0.9858341663950057</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.16737033628613</v>
+        <v>50.11158022419076</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1640,22 +1640,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2020655181236626</v>
+        <v>0.2017994726418087</v>
       </c>
       <c r="C5">
-        <v>27.53774777366362</v>
+        <v>27.28378200011144</v>
       </c>
       <c r="D5">
-        <v>28.38674777366362</v>
+        <v>28.41578200011144</v>
       </c>
       <c r="E5">
-        <v>0.849</v>
+        <v>1.132</v>
       </c>
       <c r="F5">
-        <v>0.849</v>
+        <v>1.132</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1676,28 +1676,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M5">
-        <v>0.0427047</v>
+        <v>0.0569396</v>
       </c>
       <c r="N5">
-        <v>2.097295299999999</v>
+        <v>2.083060399999999</v>
       </c>
       <c r="O5">
-        <v>0.3145942949999999</v>
+        <v>0.3124590599999998</v>
       </c>
       <c r="P5">
-        <v>1.782701004999999</v>
+        <v>1.770601339999999</v>
       </c>
       <c r="Q5">
-        <v>10.742701005</v>
+        <v>10.73060134</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2069926475501676</v>
+        <v>0.2084263256685508</v>
       </c>
       <c r="T5">
-        <v>0.9858341663950057</v>
+        <v>0.9946023632960161</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.11158022419076</v>
+        <v>37.58368516814306</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1722,22 +1722,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2017994726418087</v>
+        <v>0.2015334271599548</v>
       </c>
       <c r="C6">
-        <v>27.28378200011144</v>
+        <v>27.02987568031629</v>
       </c>
       <c r="D6">
-        <v>28.41578200011144</v>
+        <v>28.44487568031629</v>
       </c>
       <c r="E6">
-        <v>1.132</v>
+        <v>1.415</v>
       </c>
       <c r="F6">
-        <v>1.132</v>
+        <v>1.415</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1758,28 +1758,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M6">
-        <v>0.0569396</v>
+        <v>0.0711745</v>
       </c>
       <c r="N6">
-        <v>2.083060399999999</v>
+        <v>2.068825499999999</v>
       </c>
       <c r="O6">
-        <v>0.3124590599999998</v>
+        <v>0.3103238249999998</v>
       </c>
       <c r="P6">
-        <v>1.770601339999999</v>
+        <v>1.758501674999999</v>
       </c>
       <c r="Q6">
-        <v>10.73060134</v>
+        <v>10.718501675</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2084263256685508</v>
+        <v>0.209890186484163</v>
       </c>
       <c r="T6">
-        <v>0.9946023632960161</v>
+        <v>1.003555153815995</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.58368516814306</v>
+        <v>30.06694813451445</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1804,22 +1804,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2015334271599548</v>
+        <v>0.201267381678101</v>
       </c>
       <c r="C7">
-        <v>27.02987568031629</v>
+        <v>26.77602899708164</v>
       </c>
       <c r="D7">
-        <v>28.44487568031629</v>
+        <v>28.47402899708164</v>
       </c>
       <c r="E7">
-        <v>1.415</v>
+        <v>1.698</v>
       </c>
       <c r="F7">
-        <v>1.415</v>
+        <v>1.698</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1840,28 +1840,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M7">
-        <v>0.0711745</v>
+        <v>0.08540940000000001</v>
       </c>
       <c r="N7">
-        <v>2.068825499999999</v>
+        <v>2.054590599999999</v>
       </c>
       <c r="O7">
-        <v>0.3103238249999998</v>
+        <v>0.3081885899999998</v>
       </c>
       <c r="P7">
-        <v>1.758501674999999</v>
+        <v>1.746402009999999</v>
       </c>
       <c r="Q7">
-        <v>10.718501675</v>
+        <v>10.70640201</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.209890186484163</v>
+        <v>0.2113851932745756</v>
       </c>
       <c r="T7">
-        <v>1.003555153815995</v>
+        <v>1.012698429240654</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.06694813451445</v>
+        <v>25.05579011209537</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1886,22 +1886,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.201267381678101</v>
+        <v>0.2010013361962472</v>
       </c>
       <c r="C8">
-        <v>26.77602899708164</v>
+        <v>26.5222421339612</v>
       </c>
       <c r="D8">
-        <v>28.47402899708164</v>
+        <v>28.5032421339612</v>
       </c>
       <c r="E8">
-        <v>1.698</v>
+        <v>1.981</v>
       </c>
       <c r="F8">
-        <v>1.698</v>
+        <v>1.981</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1922,28 +1922,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M8">
-        <v>0.0854094</v>
+        <v>0.09964429999999999</v>
       </c>
       <c r="N8">
-        <v>2.054590599999999</v>
+        <v>2.040355699999999</v>
       </c>
       <c r="O8">
-        <v>0.3081885899999998</v>
+        <v>0.3060533549999998</v>
       </c>
       <c r="P8">
-        <v>1.746402009999999</v>
+        <v>1.734302344999999</v>
       </c>
       <c r="Q8">
-        <v>10.70640201</v>
+        <v>10.694302345</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2113851932745756</v>
+        <v>0.2129123507486529</v>
       </c>
       <c r="T8">
-        <v>1.012698429240654</v>
+        <v>1.022038334244339</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.05579011209538</v>
+        <v>21.47639152465318</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1968,22 +1968,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2010013361962472</v>
+        <v>0.2007352907143934</v>
       </c>
       <c r="C9">
-        <v>26.5222421339612</v>
+        <v>26.26851527526269</v>
       </c>
       <c r="D9">
-        <v>28.5032421339612</v>
+        <v>28.53251527526269</v>
       </c>
       <c r="E9">
-        <v>1.981</v>
+        <v>2.264</v>
       </c>
       <c r="F9">
-        <v>1.981</v>
+        <v>2.264</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2004,28 +2004,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M9">
-        <v>0.09964430000000001</v>
+        <v>0.1138792</v>
       </c>
       <c r="N9">
-        <v>2.040355699999999</v>
+        <v>2.026120799999999</v>
       </c>
       <c r="O9">
-        <v>0.3060533549999998</v>
+        <v>0.3039181199999998</v>
       </c>
       <c r="P9">
-        <v>1.734302344999999</v>
+        <v>1.722202679999999</v>
       </c>
       <c r="Q9">
-        <v>10.694302345</v>
+        <v>10.68220268</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2129123507486529</v>
+        <v>0.2144727072982537</v>
       </c>
       <c r="T9">
-        <v>1.022038334244339</v>
+        <v>1.031581280661147</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.47639152465318</v>
+        <v>18.79184258407153</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2050,22 +2050,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2007352907143934</v>
+        <v>0.2004692452325395</v>
       </c>
       <c r="C10">
-        <v>26.26851527526269</v>
+        <v>26.01484860605176</v>
       </c>
       <c r="D10">
-        <v>28.53251527526269</v>
+        <v>28.56184860605176</v>
       </c>
       <c r="E10">
-        <v>2.264</v>
+        <v>2.547</v>
       </c>
       <c r="F10">
-        <v>2.264</v>
+        <v>2.547</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2086,28 +2086,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M10">
-        <v>0.1138792</v>
+        <v>0.1281141</v>
       </c>
       <c r="N10">
-        <v>2.026120799999999</v>
+        <v>2.011885899999999</v>
       </c>
       <c r="O10">
-        <v>0.3039181199999998</v>
+        <v>0.3017828849999998</v>
       </c>
       <c r="P10">
-        <v>1.722202679999999</v>
+        <v>1.710103014999999</v>
       </c>
       <c r="Q10">
-        <v>10.68220268</v>
+        <v>10.670103015</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2144727072982537</v>
+        <v>0.2160673573983951</v>
       </c>
       <c r="T10">
-        <v>1.031581280661147</v>
+        <v>1.041333962164038</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.79184258407153</v>
+        <v>16.70386007473025</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2132,22 +2132,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2004692452325395</v>
+        <v>0.2002031997506857</v>
       </c>
       <c r="C11">
-        <v>26.01484860605176</v>
+        <v>25.76124231215591</v>
       </c>
       <c r="D11">
-        <v>28.56184860605176</v>
+        <v>28.59124231215591</v>
       </c>
       <c r="E11">
-        <v>2.547</v>
+        <v>2.83</v>
       </c>
       <c r="F11">
-        <v>2.547</v>
+        <v>2.83</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2168,28 +2168,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M11">
-        <v>0.1281141</v>
+        <v>0.142349</v>
       </c>
       <c r="N11">
-        <v>2.011885899999999</v>
+        <v>1.997650999999999</v>
       </c>
       <c r="O11">
-        <v>0.3017828849999998</v>
+        <v>0.2996476499999998</v>
       </c>
       <c r="P11">
-        <v>1.710103014999999</v>
+        <v>1.698003349999999</v>
       </c>
       <c r="Q11">
-        <v>10.670103015</v>
+        <v>10.65800335</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2160673573983951</v>
+        <v>0.2176974441674286</v>
       </c>
       <c r="T11">
-        <v>1.041333962164038</v>
+        <v>1.05130336992255</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.70386007473025</v>
+        <v>15.03347406725723</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2214,22 +2214,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2002031997506857</v>
+        <v>0.1999371542688319</v>
       </c>
       <c r="C12">
-        <v>25.76124231215591</v>
+        <v>25.50769658016835</v>
       </c>
       <c r="D12">
-        <v>28.59124231215591</v>
+        <v>28.62069658016835</v>
       </c>
       <c r="E12">
-        <v>2.83</v>
+        <v>3.113</v>
       </c>
       <c r="F12">
-        <v>2.83</v>
+        <v>3.113</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2250,28 +2250,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M12">
-        <v>0.142349</v>
+        <v>0.1565839</v>
       </c>
       <c r="N12">
-        <v>1.997650999999999</v>
+        <v>1.983416099999999</v>
       </c>
       <c r="O12">
-        <v>0.2996476499999998</v>
+        <v>0.2975124149999998</v>
       </c>
       <c r="P12">
-        <v>1.698003349999999</v>
+        <v>1.685903684999999</v>
       </c>
       <c r="Q12">
-        <v>10.65800335</v>
+        <v>10.645903685</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2176974441674286</v>
+        <v>0.2193641620998111</v>
       </c>
       <c r="T12">
-        <v>1.05130336992255</v>
+        <v>1.061496809316084</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.03347406725723</v>
+        <v>13.66679460659748</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2296,22 +2296,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1999371542688319</v>
+        <v>0.199824108786978</v>
       </c>
       <c r="C13">
-        <v>25.50769658016835</v>
+        <v>25.23723038353706</v>
       </c>
       <c r="D13">
-        <v>28.62069658016835</v>
+        <v>28.63323038353706</v>
       </c>
       <c r="E13">
-        <v>3.113</v>
+        <v>3.396</v>
       </c>
       <c r="F13">
-        <v>3.113</v>
+        <v>3.396</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2332,45 +2332,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M13">
-        <v>0.1565839</v>
+        <v>0.1759128</v>
       </c>
       <c r="N13">
-        <v>1.983416099999999</v>
+        <v>1.964087199999999</v>
       </c>
       <c r="O13">
-        <v>0.2975124149999998</v>
+        <v>0.2946130799999998</v>
       </c>
       <c r="P13">
-        <v>1.685903684999999</v>
+        <v>1.669474119999999</v>
       </c>
       <c r="Q13">
-        <v>10.645903685</v>
+        <v>10.62947412</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2193641620998111</v>
+        <v>0.2210687599852023</v>
       </c>
       <c r="T13">
-        <v>1.061496809316084</v>
+        <v>1.071921917786744</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.66679460659748</v>
+        <v>12.16511817218531</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2378,22 +2378,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.199824108786978</v>
+        <v>0.1995708133051242</v>
       </c>
       <c r="C14">
-        <v>25.23723038353706</v>
+        <v>24.98235415868131</v>
       </c>
       <c r="D14">
-        <v>28.63323038353706</v>
+        <v>28.66135415868131</v>
       </c>
       <c r="E14">
-        <v>3.396</v>
+        <v>3.679</v>
       </c>
       <c r="F14">
-        <v>3.396</v>
+        <v>3.679</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2414,28 +2414,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M14">
-        <v>0.1759128</v>
+        <v>0.1905722</v>
       </c>
       <c r="N14">
-        <v>1.964087199999999</v>
+        <v>1.949427799999999</v>
       </c>
       <c r="O14">
-        <v>0.2946130799999998</v>
+        <v>0.2924141699999998</v>
       </c>
       <c r="P14">
-        <v>1.669474119999999</v>
+        <v>1.657013629999999</v>
       </c>
       <c r="Q14">
-        <v>10.62947412</v>
+        <v>10.61701363</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2210687599852023</v>
+        <v>0.2228125440288784</v>
       </c>
       <c r="T14">
-        <v>1.071921917786744</v>
+        <v>1.082586683923396</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.16511817218531</v>
+        <v>11.22933985124797</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2460,22 +2460,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1995708133051242</v>
+        <v>0.1993175178232704</v>
       </c>
       <c r="C15">
-        <v>24.98235415868131</v>
+        <v>24.72753323491143</v>
       </c>
       <c r="D15">
-        <v>28.66135415868131</v>
+        <v>28.68953323491143</v>
       </c>
       <c r="E15">
-        <v>3.679</v>
+        <v>3.962000000000001</v>
       </c>
       <c r="F15">
-        <v>3.679</v>
+        <v>3.962000000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2496,28 +2496,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M15">
-        <v>0.1905722</v>
+        <v>0.2052316</v>
       </c>
       <c r="N15">
-        <v>1.949427799999999</v>
+        <v>1.934768399999999</v>
       </c>
       <c r="O15">
-        <v>0.2924141699999998</v>
+        <v>0.2902152599999998</v>
       </c>
       <c r="P15">
-        <v>1.657013629999999</v>
+        <v>1.644553139999999</v>
       </c>
       <c r="Q15">
-        <v>10.61701363</v>
+        <v>10.60455314</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2228125440288784</v>
+        <v>0.2245968811898492</v>
       </c>
       <c r="T15">
-        <v>1.082586683923396</v>
+        <v>1.093499467877179</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.22933985124797</v>
+        <v>10.4272441475874</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2542,22 +2542,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1993175178232704</v>
+        <v>0.1992809723414165</v>
       </c>
       <c r="C16">
-        <v>24.72753323491143</v>
+        <v>24.44860348775319</v>
       </c>
       <c r="D16">
-        <v>28.68953323491143</v>
+        <v>28.69360348775319</v>
       </c>
       <c r="E16">
-        <v>3.962000000000001</v>
+        <v>4.245000000000001</v>
       </c>
       <c r="F16">
-        <v>3.962000000000001</v>
+        <v>4.245000000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2578,45 +2578,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M16">
-        <v>0.2052316</v>
+        <v>0.2271075</v>
       </c>
       <c r="N16">
-        <v>1.934768399999999</v>
+        <v>1.912892499999999</v>
       </c>
       <c r="O16">
-        <v>0.2902152599999998</v>
+        <v>0.2869338749999998</v>
       </c>
       <c r="P16">
-        <v>1.644553139999999</v>
+        <v>1.625958624999999</v>
       </c>
       <c r="Q16">
-        <v>10.60455314</v>
+        <v>10.585958625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2245968811898492</v>
+        <v>0.2264232027546077</v>
       </c>
       <c r="T16">
-        <v>1.093499467877179</v>
+        <v>1.10466902321811</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.4272441475874</v>
+        <v>9.422850412249698</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2624,22 +2624,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1992809723414165</v>
+        <v>0.1990421268595627</v>
       </c>
       <c r="C17">
-        <v>24.44860348775319</v>
+        <v>24.19223336766508</v>
       </c>
       <c r="D17">
-        <v>28.69360348775319</v>
+        <v>28.72023336766507</v>
       </c>
       <c r="E17">
-        <v>4.245</v>
+        <v>4.528</v>
       </c>
       <c r="F17">
-        <v>4.245</v>
+        <v>4.528</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2660,28 +2660,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M17">
-        <v>0.2271075</v>
+        <v>0.242248</v>
       </c>
       <c r="N17">
-        <v>1.912892499999999</v>
+        <v>1.897751999999999</v>
       </c>
       <c r="O17">
-        <v>0.2869338749999998</v>
+        <v>0.2846627999999998</v>
       </c>
       <c r="P17">
-        <v>1.625958624999999</v>
+        <v>1.613089199999999</v>
       </c>
       <c r="Q17">
-        <v>10.585958625</v>
+        <v>10.5730892</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2264232027546077</v>
+        <v>0.2282930081661461</v>
       </c>
       <c r="T17">
-        <v>1.10466902321811</v>
+        <v>1.116104520352874</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.4228504122497</v>
+        <v>8.833922261484094</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2706,22 +2706,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1990421268595627</v>
+        <v>0.1988032813777089</v>
       </c>
       <c r="C18">
-        <v>24.19223336766508</v>
+        <v>23.9359127226638</v>
       </c>
       <c r="D18">
-        <v>28.72023336766507</v>
+        <v>28.7469127226638</v>
       </c>
       <c r="E18">
-        <v>4.528</v>
+        <v>4.811000000000001</v>
       </c>
       <c r="F18">
-        <v>4.528</v>
+        <v>4.811000000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2742,28 +2742,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M18">
-        <v>0.242248</v>
+        <v>0.2573885</v>
       </c>
       <c r="N18">
-        <v>1.897751999999999</v>
+        <v>1.882611499999999</v>
       </c>
       <c r="O18">
-        <v>0.2846627999999998</v>
+        <v>0.2823917249999998</v>
       </c>
       <c r="P18">
-        <v>1.613089199999999</v>
+        <v>1.600219774999999</v>
       </c>
       <c r="Q18">
-        <v>10.5730892</v>
+        <v>10.560219775</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2282930081661461</v>
+        <v>0.2302078691297697</v>
       </c>
       <c r="T18">
-        <v>1.116104520352874</v>
+        <v>1.127815571635462</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.833922261484094</v>
+        <v>8.314279775514441</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2788,22 +2788,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1988032813777089</v>
+        <v>0.198564435895855</v>
       </c>
       <c r="C19">
-        <v>23.9359127226638</v>
+        <v>23.6796416907556</v>
       </c>
       <c r="D19">
-        <v>28.7469127226638</v>
+        <v>28.7736416907556</v>
       </c>
       <c r="E19">
-        <v>4.811000000000001</v>
+        <v>5.094</v>
       </c>
       <c r="F19">
-        <v>4.811000000000001</v>
+        <v>5.094</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2824,28 +2824,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M19">
-        <v>0.2573885</v>
+        <v>0.272529</v>
       </c>
       <c r="N19">
-        <v>1.882611499999999</v>
+        <v>1.867470999999999</v>
       </c>
       <c r="O19">
-        <v>0.2823917249999998</v>
+        <v>0.2801206499999998</v>
       </c>
       <c r="P19">
-        <v>1.600219774999999</v>
+        <v>1.587350349999999</v>
       </c>
       <c r="Q19">
-        <v>10.560219775</v>
+        <v>10.54735035</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2302078691297697</v>
+        <v>0.2321694340193354</v>
       </c>
       <c r="T19">
-        <v>1.127815571635462</v>
+        <v>1.139812258315187</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.314279775514441</v>
+        <v>7.852375343541416</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2870,22 +2870,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.198564435895855</v>
+        <v>0.1984547904140012</v>
       </c>
       <c r="C20">
-        <v>23.6796416907556</v>
+        <v>23.40892866469353</v>
       </c>
       <c r="D20">
-        <v>28.7736416907556</v>
+        <v>28.78592866469353</v>
       </c>
       <c r="E20">
-        <v>5.094</v>
+        <v>5.377</v>
       </c>
       <c r="F20">
-        <v>5.094</v>
+        <v>5.377</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2906,45 +2906,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M20">
-        <v>0.272529</v>
+        <v>0.2919711</v>
       </c>
       <c r="N20">
-        <v>1.867470999999999</v>
+        <v>1.848028899999999</v>
       </c>
       <c r="O20">
-        <v>0.2801206499999998</v>
+        <v>0.2772043349999998</v>
       </c>
       <c r="P20">
-        <v>1.587350349999999</v>
+        <v>1.570824564999999</v>
       </c>
       <c r="Q20">
-        <v>10.54735035</v>
+        <v>10.530824565</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2321694340193354</v>
+        <v>0.234179432609878</v>
       </c>
       <c r="T20">
-        <v>1.139812258315187</v>
+        <v>1.152105159480831</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.852375343541416</v>
+        <v>7.329492542241335</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2952,22 +2952,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1984547904140012</v>
+        <v>0.1982227449321473</v>
       </c>
       <c r="C21">
-        <v>23.40892866469353</v>
+        <v>23.15196653046132</v>
       </c>
       <c r="D21">
-        <v>28.78592866469353</v>
+        <v>28.81196653046132</v>
       </c>
       <c r="E21">
-        <v>5.377</v>
+        <v>5.66</v>
       </c>
       <c r="F21">
-        <v>5.377</v>
+        <v>5.66</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2988,28 +2988,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M21">
-        <v>0.2919711</v>
+        <v>0.307338</v>
       </c>
       <c r="N21">
-        <v>1.848028899999999</v>
+        <v>1.832661999999999</v>
       </c>
       <c r="O21">
-        <v>0.2772043349999998</v>
+        <v>0.2748992999999998</v>
       </c>
       <c r="P21">
-        <v>1.570824564999999</v>
+        <v>1.557762699999999</v>
       </c>
       <c r="Q21">
-        <v>10.530824565</v>
+        <v>10.5177627</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.234179432609878</v>
+        <v>0.2362396811651842</v>
       </c>
       <c r="T21">
-        <v>1.152105159480831</v>
+        <v>1.164705383175616</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.329492542241335</v>
+        <v>6.963017915129267</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3034,22 +3034,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1982227449321473</v>
+        <v>0.1979906994502935</v>
       </c>
       <c r="C22">
-        <v>23.15196653046132</v>
+        <v>22.89505154317125</v>
       </c>
       <c r="D22">
-        <v>28.81196653046132</v>
+        <v>28.83805154317125</v>
       </c>
       <c r="E22">
-        <v>5.66</v>
+        <v>5.943000000000001</v>
       </c>
       <c r="F22">
-        <v>5.66</v>
+        <v>5.943000000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3070,28 +3070,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M22">
-        <v>0.307338</v>
+        <v>0.3227049</v>
       </c>
       <c r="N22">
-        <v>1.832661999999999</v>
+        <v>1.817295099999999</v>
       </c>
       <c r="O22">
-        <v>0.2748992999999998</v>
+        <v>0.2725942649999998</v>
       </c>
       <c r="P22">
-        <v>1.557762699999999</v>
+        <v>1.544700834999999</v>
       </c>
       <c r="Q22">
-        <v>10.5177627</v>
+        <v>10.504700835</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2362396811651842</v>
+        <v>0.2383520879117639</v>
       </c>
       <c r="T22">
-        <v>1.164705383175616</v>
+        <v>1.177624599875333</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.963017915129267</v>
+        <v>6.631445633456445</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3116,22 +3116,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1979906994502935</v>
+        <v>0.1977586539684397</v>
       </c>
       <c r="C23">
-        <v>22.89505154317126</v>
+        <v>22.63818383099331</v>
       </c>
       <c r="D23">
-        <v>28.83805154317126</v>
+        <v>28.8641838309933</v>
       </c>
       <c r="E23">
-        <v>5.943</v>
+        <v>6.226</v>
       </c>
       <c r="F23">
-        <v>5.943</v>
+        <v>6.226</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3152,28 +3152,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M23">
-        <v>0.3227049</v>
+        <v>0.3380718</v>
       </c>
       <c r="N23">
-        <v>1.817295099999999</v>
+        <v>1.801928199999999</v>
       </c>
       <c r="O23">
-        <v>0.2725942649999998</v>
+        <v>0.2702892299999998</v>
       </c>
       <c r="P23">
-        <v>1.544700834999999</v>
+        <v>1.531638969999999</v>
       </c>
       <c r="Q23">
-        <v>10.504700835</v>
+        <v>10.49163897</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2383520879117639</v>
+        <v>0.240518658933897</v>
       </c>
       <c r="T23">
-        <v>1.177624599875333</v>
+        <v>1.190875078541709</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.631445633456446</v>
+        <v>6.330016286481152</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3198,22 +3198,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1977586539684397</v>
+        <v>0.1977221084865858</v>
       </c>
       <c r="C24">
-        <v>22.63818383099331</v>
+        <v>22.35930379442997</v>
       </c>
       <c r="D24">
-        <v>28.8641838309933</v>
+        <v>28.86830379442997</v>
       </c>
       <c r="E24">
-        <v>6.226</v>
+        <v>6.509</v>
       </c>
       <c r="F24">
-        <v>6.226</v>
+        <v>6.509</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3234,45 +3234,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M24">
-        <v>0.3380718</v>
+        <v>0.3599477</v>
       </c>
       <c r="N24">
-        <v>1.801928199999999</v>
+        <v>1.780052299999999</v>
       </c>
       <c r="O24">
-        <v>0.2702892299999998</v>
+        <v>0.2670078449999998</v>
       </c>
       <c r="P24">
-        <v>1.531638969999999</v>
+        <v>1.513044454999999</v>
       </c>
       <c r="Q24">
-        <v>10.49163897</v>
+        <v>10.473044455</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.240518658933897</v>
+        <v>0.2427415045280335</v>
       </c>
       <c r="T24">
-        <v>1.190875078541709</v>
+        <v>1.204469725485133</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.330016286481152</v>
+        <v>5.945308165602944</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3280,22 +3280,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1977221084865858</v>
+        <v>0.197498563004732</v>
       </c>
       <c r="C25">
-        <v>22.35930379442997</v>
+        <v>22.10153086959922</v>
       </c>
       <c r="D25">
-        <v>28.86830379442997</v>
+        <v>28.89353086959922</v>
       </c>
       <c r="E25">
-        <v>6.509</v>
+        <v>6.792000000000001</v>
       </c>
       <c r="F25">
-        <v>6.509</v>
+        <v>6.792000000000001</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3316,28 +3316,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M25">
-        <v>0.3599477</v>
+        <v>0.3755976</v>
       </c>
       <c r="N25">
-        <v>1.780052299999999</v>
+        <v>1.764402399999999</v>
       </c>
       <c r="O25">
-        <v>0.2670078449999998</v>
+        <v>0.2646603599999998</v>
       </c>
       <c r="P25">
-        <v>1.513044454999999</v>
+        <v>1.499742039999999</v>
       </c>
       <c r="Q25">
-        <v>10.473044455</v>
+        <v>10.45974204</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2427415045280335</v>
+        <v>0.2450228460588579</v>
       </c>
       <c r="T25">
-        <v>1.204469725485133</v>
+        <v>1.21842212629549</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.945308165602944</v>
+        <v>5.697586992036154</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3362,22 +3362,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.197498563004732</v>
+        <v>0.1972750175228781</v>
       </c>
       <c r="C26">
-        <v>22.10153086959922</v>
+        <v>21.84380207357817</v>
       </c>
       <c r="D26">
-        <v>28.89353086959922</v>
+        <v>28.91880207357817</v>
       </c>
       <c r="E26">
-        <v>6.792</v>
+        <v>7.075</v>
       </c>
       <c r="F26">
-        <v>6.792</v>
+        <v>7.075</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3398,28 +3398,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M26">
-        <v>0.3755976</v>
+        <v>0.3912475</v>
       </c>
       <c r="N26">
-        <v>1.764402399999999</v>
+        <v>1.748752499999999</v>
       </c>
       <c r="O26">
-        <v>0.2646603599999998</v>
+        <v>0.2623128749999998</v>
       </c>
       <c r="P26">
-        <v>1.499742039999999</v>
+        <v>1.486439624999999</v>
       </c>
       <c r="Q26">
-        <v>10.45974204</v>
+        <v>10.446439625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2450228460588579</v>
+        <v>0.2473650233638375</v>
       </c>
       <c r="T26">
-        <v>1.21842212629549</v>
+        <v>1.232746591127456</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.697586992036156</v>
+        <v>5.469683512354708</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3444,22 +3444,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1972750175228781</v>
+        <v>0.1970514720410243</v>
       </c>
       <c r="C27">
-        <v>21.84380207357817</v>
+        <v>21.58611752225755</v>
       </c>
       <c r="D27">
-        <v>28.91880207357817</v>
+        <v>28.94411752225755</v>
       </c>
       <c r="E27">
-        <v>7.075</v>
+        <v>7.358000000000001</v>
       </c>
       <c r="F27">
-        <v>7.075</v>
+        <v>7.358000000000001</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3480,28 +3480,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M27">
-        <v>0.3912475</v>
+        <v>0.4068974</v>
       </c>
       <c r="N27">
-        <v>1.748752499999999</v>
+        <v>1.733102599999999</v>
       </c>
       <c r="O27">
-        <v>0.2623128749999998</v>
+        <v>0.2599653899999998</v>
       </c>
       <c r="P27">
-        <v>1.486439624999999</v>
+        <v>1.473137209999999</v>
       </c>
       <c r="Q27">
-        <v>10.446439625</v>
+        <v>10.43313721</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2473650233638375</v>
+        <v>0.249770502758141</v>
       </c>
       <c r="T27">
-        <v>1.232746591127456</v>
+        <v>1.247458203657584</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.469683512354708</v>
+        <v>5.259311069571835</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3526,22 +3526,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1970514720410243</v>
+        <v>0.1968279265591705</v>
       </c>
       <c r="C28">
-        <v>21.58611752225755</v>
+        <v>21.32847733193428</v>
       </c>
       <c r="D28">
-        <v>28.94411752225755</v>
+        <v>28.96947733193428</v>
       </c>
       <c r="E28">
-        <v>7.358000000000001</v>
+        <v>7.641000000000001</v>
       </c>
       <c r="F28">
-        <v>7.358000000000001</v>
+        <v>7.641000000000001</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3562,28 +3562,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M28">
-        <v>0.4068974</v>
+        <v>0.4225473000000001</v>
       </c>
       <c r="N28">
-        <v>1.733102599999999</v>
+        <v>1.717452699999999</v>
       </c>
       <c r="O28">
-        <v>0.2599653899999998</v>
+        <v>0.2576179049999998</v>
       </c>
       <c r="P28">
-        <v>1.473137209999999</v>
+        <v>1.459834794999999</v>
       </c>
       <c r="Q28">
-        <v>10.43313721</v>
+        <v>10.419834795</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.249770502758141</v>
+        <v>0.2522418856974938</v>
       </c>
       <c r="T28">
-        <v>1.247458203657584</v>
+        <v>1.26257287406525</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.259311069571835</v>
+        <v>5.064521770698803</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3608,22 +3608,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1968279265591705</v>
+        <v>0.1966043810773166</v>
       </c>
       <c r="C29">
-        <v>21.32847733193428</v>
+        <v>21.07088161931323</v>
       </c>
       <c r="D29">
-        <v>28.96947733193428</v>
+        <v>28.99488161931323</v>
       </c>
       <c r="E29">
-        <v>7.641000000000001</v>
+        <v>7.924000000000001</v>
       </c>
       <c r="F29">
-        <v>7.641000000000001</v>
+        <v>7.924000000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3644,28 +3644,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M29">
-        <v>0.4225473000000001</v>
+        <v>0.4381972000000001</v>
       </c>
       <c r="N29">
-        <v>1.717452699999999</v>
+        <v>1.701802799999999</v>
       </c>
       <c r="O29">
-        <v>0.2576179049999998</v>
+        <v>0.2552704199999998</v>
       </c>
       <c r="P29">
-        <v>1.459834794999999</v>
+        <v>1.446532379999999</v>
       </c>
       <c r="Q29">
-        <v>10.419834795</v>
+        <v>10.40653238</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2522418856974938</v>
+        <v>0.2547819181629398</v>
       </c>
       <c r="T29">
-        <v>1.26257287406525</v>
+        <v>1.278107396428684</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.064521770698803</v>
+        <v>4.883645993173847</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3690,22 +3690,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1966043810773166</v>
+        <v>0.1963808355954628</v>
       </c>
       <c r="C30">
-        <v>21.07088161931323</v>
+        <v>20.81333050150896</v>
       </c>
       <c r="D30">
-        <v>28.99488161931323</v>
+        <v>29.02033050150896</v>
       </c>
       <c r="E30">
-        <v>7.924000000000001</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="F30">
-        <v>7.924000000000001</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3726,28 +3726,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M30">
-        <v>0.4381972000000001</v>
+        <v>0.4538471000000001</v>
       </c>
       <c r="N30">
-        <v>1.701802799999999</v>
+        <v>1.686152899999999</v>
       </c>
       <c r="O30">
-        <v>0.2552704199999998</v>
+        <v>0.2529229349999998</v>
       </c>
       <c r="P30">
-        <v>1.446532379999999</v>
+        <v>1.433229964999999</v>
       </c>
       <c r="Q30">
-        <v>10.40653238</v>
+        <v>10.393229965</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2547819181629398</v>
+        <v>0.25739350083868</v>
       </c>
       <c r="T30">
-        <v>1.278107396428684</v>
+        <v>1.294079510971369</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.883645993173847</v>
+        <v>4.715244407202334</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3772,22 +3772,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1963808355954628</v>
+        <v>0.1961572901136089</v>
       </c>
       <c r="C31">
-        <v>20.81333050150896</v>
+        <v>20.55582409604758</v>
       </c>
       <c r="D31">
-        <v>29.02033050150896</v>
+        <v>29.04582409604758</v>
       </c>
       <c r="E31">
-        <v>8.206999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="F31">
-        <v>8.206999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3808,28 +3808,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M31">
-        <v>0.4538470999999999</v>
+        <v>0.4694970000000001</v>
       </c>
       <c r="N31">
-        <v>1.686152899999999</v>
+        <v>1.670502999999999</v>
       </c>
       <c r="O31">
-        <v>0.2529229349999998</v>
+        <v>0.2505754499999998</v>
       </c>
       <c r="P31">
-        <v>1.433229964999999</v>
+        <v>1.419927549999999</v>
       </c>
       <c r="Q31">
-        <v>10.393229965</v>
+        <v>10.37992755</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.25739350083868</v>
+        <v>0.2600797001622985</v>
       </c>
       <c r="T31">
-        <v>1.294079510971369</v>
+        <v>1.310507971643845</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.715244407202336</v>
+        <v>4.558069593628923</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3854,22 +3854,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1961572901136089</v>
+        <v>0.1965924946317551</v>
       </c>
       <c r="C32">
-        <v>20.55582409604758</v>
+        <v>20.22323367337513</v>
       </c>
       <c r="D32">
-        <v>29.04582409604758</v>
+        <v>28.99623367337513</v>
       </c>
       <c r="E32">
-        <v>8.49</v>
+        <v>8.773</v>
       </c>
       <c r="F32">
-        <v>8.49</v>
+        <v>8.773</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3890,45 +3890,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M32">
-        <v>0.4694970000000001</v>
+        <v>0.5070794000000001</v>
       </c>
       <c r="N32">
-        <v>1.670502999999999</v>
+        <v>1.632920599999999</v>
       </c>
       <c r="O32">
-        <v>0.2505754499999998</v>
+        <v>0.2449380899999998</v>
       </c>
       <c r="P32">
-        <v>1.419927549999999</v>
+        <v>1.387982509999999</v>
       </c>
       <c r="Q32">
-        <v>10.37992755</v>
+        <v>10.34798251</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2600797001622985</v>
+        <v>0.262843760335877</v>
       </c>
       <c r="T32">
-        <v>1.310507971643845</v>
+        <v>1.327412619582191</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.558069593628923</v>
+        <v>4.220246375616912</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3936,22 +3936,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1965924946317551</v>
+        <v>0.1963901991499013</v>
       </c>
       <c r="C33">
-        <v>20.22323367337513</v>
+        <v>19.96326363863419</v>
       </c>
       <c r="D33">
-        <v>28.99623367337513</v>
+        <v>29.01926363863419</v>
       </c>
       <c r="E33">
-        <v>8.773</v>
+        <v>9.056000000000001</v>
       </c>
       <c r="F33">
-        <v>8.773</v>
+        <v>9.056000000000001</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3972,28 +3972,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M33">
-        <v>0.5070794000000001</v>
+        <v>0.5234368000000001</v>
       </c>
       <c r="N33">
-        <v>1.632920599999999</v>
+        <v>1.616563199999999</v>
       </c>
       <c r="O33">
-        <v>0.2449380899999998</v>
+        <v>0.2424844799999998</v>
       </c>
       <c r="P33">
-        <v>1.387982509999999</v>
+        <v>1.374078719999999</v>
       </c>
       <c r="Q33">
-        <v>10.34798251</v>
+        <v>10.33407872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.262843760335877</v>
+        <v>0.2656891163969137</v>
       </c>
       <c r="T33">
-        <v>1.327412619582191</v>
+        <v>1.344814463048134</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.220246375616912</v>
+        <v>4.088363676378883</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4018,22 +4018,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1963901991499013</v>
+        <v>0.1971696536680475</v>
       </c>
       <c r="C34">
-        <v>19.96326363863419</v>
+        <v>19.59172850294701</v>
       </c>
       <c r="D34">
-        <v>29.01926363863419</v>
+        <v>28.93072850294702</v>
       </c>
       <c r="E34">
-        <v>9.056000000000001</v>
+        <v>9.339</v>
       </c>
       <c r="F34">
-        <v>9.056000000000001</v>
+        <v>9.339</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4054,45 +4054,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M34">
-        <v>0.5234368000000001</v>
+        <v>0.5724807000000001</v>
       </c>
       <c r="N34">
-        <v>1.616563199999999</v>
+        <v>1.567519299999999</v>
       </c>
       <c r="O34">
-        <v>0.2424844799999998</v>
+        <v>0.2351278949999998</v>
       </c>
       <c r="P34">
-        <v>1.374078719999999</v>
+        <v>1.332391404999999</v>
       </c>
       <c r="Q34">
-        <v>10.33407872</v>
+        <v>10.292391405</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2656891163969137</v>
+        <v>0.2686194084597723</v>
       </c>
       <c r="T34">
-        <v>1.344814463048134</v>
+        <v>1.362735764527987</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.088363676378883</v>
+        <v>3.73811728500192</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4100,22 +4100,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1971696536680475</v>
+        <v>0.1969971081861936</v>
       </c>
       <c r="C35">
-        <v>19.59172850294701</v>
+        <v>19.32828066825999</v>
       </c>
       <c r="D35">
-        <v>28.93072850294702</v>
+        <v>28.95028066825999</v>
       </c>
       <c r="E35">
-        <v>9.339</v>
+        <v>9.622000000000002</v>
       </c>
       <c r="F35">
-        <v>9.339</v>
+        <v>9.622000000000002</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4136,28 +4136,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M35">
-        <v>0.5724807000000001</v>
+        <v>0.5898286000000001</v>
       </c>
       <c r="N35">
-        <v>1.567519299999999</v>
+        <v>1.550171399999999</v>
       </c>
       <c r="O35">
-        <v>0.2351278949999998</v>
+        <v>0.2325257099999998</v>
       </c>
       <c r="P35">
-        <v>1.332391404999999</v>
+        <v>1.317645689999999</v>
       </c>
       <c r="Q35">
-        <v>10.292391405</v>
+        <v>10.27764569</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2686194084597723</v>
+        <v>0.2716384972518086</v>
       </c>
       <c r="T35">
-        <v>1.362735764527987</v>
+        <v>1.381200135749653</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.73811728500192</v>
+        <v>3.628172658972451</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4182,22 +4182,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1969971081861936</v>
+        <v>0.1968245627043398</v>
       </c>
       <c r="C36">
-        <v>19.32828066825999</v>
+        <v>19.0648592792052</v>
       </c>
       <c r="D36">
-        <v>28.95028066825999</v>
+        <v>28.9698592792052</v>
       </c>
       <c r="E36">
-        <v>9.622000000000002</v>
+        <v>9.905000000000001</v>
       </c>
       <c r="F36">
-        <v>9.622000000000002</v>
+        <v>9.905000000000001</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4218,28 +4218,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M36">
-        <v>0.5898286000000001</v>
+        <v>0.6071765000000001</v>
       </c>
       <c r="N36">
-        <v>1.550171399999999</v>
+        <v>1.532823499999999</v>
       </c>
       <c r="O36">
-        <v>0.2325257099999998</v>
+        <v>0.2299235249999998</v>
       </c>
       <c r="P36">
-        <v>1.317645689999999</v>
+        <v>1.302899974999999</v>
       </c>
       <c r="Q36">
-        <v>10.27764569</v>
+        <v>10.262899975</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2716384972518086</v>
+        <v>0.2747504810835997</v>
       </c>
       <c r="T36">
-        <v>1.381200135749653</v>
+        <v>1.400232641470448</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.628172658972451</v>
+        <v>3.52451058300181</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4264,22 +4264,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1968245627043398</v>
+        <v>0.1975088172224859</v>
       </c>
       <c r="C37">
-        <v>19.0648592792052</v>
+        <v>18.70437271781091</v>
       </c>
       <c r="D37">
-        <v>28.9698592792052</v>
+        <v>28.89237271781091</v>
       </c>
       <c r="E37">
-        <v>9.905000000000001</v>
+        <v>10.188</v>
       </c>
       <c r="F37">
-        <v>9.905000000000001</v>
+        <v>10.188</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4300,45 +4300,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M37">
-        <v>0.6071765000000001</v>
+        <v>0.6530508</v>
       </c>
       <c r="N37">
-        <v>1.532823499999999</v>
+        <v>1.486949199999999</v>
       </c>
       <c r="O37">
-        <v>0.2299235249999998</v>
+        <v>0.2230423799999998</v>
       </c>
       <c r="P37">
-        <v>1.302899974999999</v>
+        <v>1.263906819999999</v>
       </c>
       <c r="Q37">
-        <v>10.262899975</v>
+        <v>10.22390682</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2747504810835997</v>
+        <v>0.2779597144101343</v>
       </c>
       <c r="T37">
-        <v>1.400232641470448</v>
+        <v>1.419859912995017</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.15</v>
       </c>
       <c r="W37">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.52451058300181</v>
+        <v>3.276927307952151</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4346,22 +4346,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1975088172224859</v>
+        <v>0.1973600717406321</v>
       </c>
       <c r="C38">
-        <v>18.70437271781091</v>
+        <v>18.43818171913075</v>
       </c>
       <c r="D38">
-        <v>28.89237271781091</v>
+        <v>28.90918171913075</v>
       </c>
       <c r="E38">
-        <v>10.188</v>
+        <v>10.471</v>
       </c>
       <c r="F38">
-        <v>10.188</v>
+        <v>10.471</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4382,28 +4382,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M38">
-        <v>0.6530508</v>
+        <v>0.6711911</v>
       </c>
       <c r="N38">
-        <v>1.486949199999999</v>
+        <v>1.468808899999999</v>
       </c>
       <c r="O38">
-        <v>0.2230423799999998</v>
+        <v>0.2203213349999998</v>
       </c>
       <c r="P38">
-        <v>1.263906819999999</v>
+        <v>1.248487564999999</v>
       </c>
       <c r="Q38">
-        <v>10.22390682</v>
+        <v>10.208487565</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2779597144101343</v>
+        <v>0.2812708281597335</v>
       </c>
       <c r="T38">
-        <v>1.419859912995017</v>
+        <v>1.440110272504493</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.276927307952151</v>
+        <v>3.188361705034525</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4428,22 +4428,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1973600717406321</v>
+        <v>0.1972113262587783</v>
       </c>
       <c r="C39">
-        <v>18.43818171913075</v>
+        <v>18.17201029011358</v>
       </c>
       <c r="D39">
-        <v>28.90918171913075</v>
+        <v>28.92601029011358</v>
       </c>
       <c r="E39">
-        <v>10.471</v>
+        <v>10.754</v>
       </c>
       <c r="F39">
-        <v>10.471</v>
+        <v>10.754</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4464,28 +4464,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M39">
-        <v>0.6711911</v>
+        <v>0.6893314</v>
       </c>
       <c r="N39">
-        <v>1.468808899999999</v>
+        <v>1.450668599999999</v>
       </c>
       <c r="O39">
-        <v>0.2203213349999998</v>
+        <v>0.2176002899999998</v>
       </c>
       <c r="P39">
-        <v>1.248487564999999</v>
+        <v>1.233068309999999</v>
       </c>
       <c r="Q39">
-        <v>10.208487565</v>
+        <v>10.19306831</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2812708281597335</v>
+        <v>0.2846887520302876</v>
       </c>
       <c r="T39">
-        <v>1.440110272504493</v>
+        <v>1.461013869417501</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.188361705034525</v>
+        <v>3.10445744963888</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4510,22 +4510,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1972113262587783</v>
+        <v>0.1970625807769244</v>
       </c>
       <c r="C40">
-        <v>18.17201029011358</v>
+        <v>17.90585846495491</v>
       </c>
       <c r="D40">
-        <v>28.92601029011358</v>
+        <v>28.94285846495491</v>
       </c>
       <c r="E40">
-        <v>10.754</v>
+        <v>11.037</v>
       </c>
       <c r="F40">
-        <v>10.754</v>
+        <v>11.037</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4546,28 +4546,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M40">
-        <v>0.6893314</v>
+        <v>0.7074717000000001</v>
       </c>
       <c r="N40">
-        <v>1.450668599999999</v>
+        <v>1.432528299999999</v>
       </c>
       <c r="O40">
-        <v>0.2176002899999998</v>
+        <v>0.2148792449999998</v>
       </c>
       <c r="P40">
-        <v>1.233068309999999</v>
+        <v>1.217649054999999</v>
       </c>
       <c r="Q40">
-        <v>10.19306831</v>
+        <v>10.177649055</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2846887520302876</v>
+        <v>0.2882187389785646</v>
       </c>
       <c r="T40">
-        <v>1.461013869417501</v>
+        <v>1.482602830163722</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.10445744963888</v>
+        <v>3.024855976571216</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4592,22 +4592,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1970625807769244</v>
+        <v>0.1995658352950706</v>
       </c>
       <c r="C41">
-        <v>17.90585846495491</v>
+        <v>17.34190742812398</v>
       </c>
       <c r="D41">
-        <v>28.94285846495491</v>
+        <v>28.66190742812398</v>
       </c>
       <c r="E41">
-        <v>11.037</v>
+        <v>11.32</v>
       </c>
       <c r="F41">
-        <v>11.037</v>
+        <v>11.32</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4628,45 +4628,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M41">
-        <v>0.7074717000000001</v>
+        <v>0.8139080000000001</v>
       </c>
       <c r="N41">
-        <v>1.432528299999999</v>
+        <v>1.326091999999999</v>
       </c>
       <c r="O41">
-        <v>0.2148792449999998</v>
+        <v>0.1989137999999998</v>
       </c>
       <c r="P41">
-        <v>1.217649054999999</v>
+        <v>1.127178199999999</v>
       </c>
       <c r="Q41">
-        <v>10.177649055</v>
+        <v>10.0871782</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2882187389785646</v>
+        <v>0.2918663921584511</v>
       </c>
       <c r="T41">
-        <v>1.482602830163722</v>
+        <v>1.504911422934817</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.15</v>
       </c>
       <c r="W41">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.024855976571216</v>
+        <v>2.629289796881218</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4674,22 +4674,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1995658352950706</v>
+        <v>0.1994833898132168</v>
       </c>
       <c r="C42">
-        <v>17.34190742812398</v>
+        <v>17.06807374840829</v>
       </c>
       <c r="D42">
-        <v>28.66190742812398</v>
+        <v>28.67107374840829</v>
       </c>
       <c r="E42">
-        <v>11.32</v>
+        <v>11.603</v>
       </c>
       <c r="F42">
-        <v>11.32</v>
+        <v>11.603</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4710,28 +4710,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M42">
-        <v>0.8139080000000001</v>
+        <v>0.8342557000000002</v>
       </c>
       <c r="N42">
-        <v>1.326091999999999</v>
+        <v>1.305744299999999</v>
       </c>
       <c r="O42">
-        <v>0.1989137999999998</v>
+        <v>0.1958616449999998</v>
       </c>
       <c r="P42">
-        <v>1.127178199999999</v>
+        <v>1.109882654999999</v>
       </c>
       <c r="Q42">
-        <v>10.0871782</v>
+        <v>10.069882655</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2918663921584511</v>
+        <v>0.2956376945986725</v>
       </c>
       <c r="T42">
-        <v>1.504911422934817</v>
+        <v>1.527976239189678</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.629289796881218</v>
+        <v>2.565160777445091</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4756,22 +4756,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1994833898132168</v>
+        <v>0.1994009443313629</v>
       </c>
       <c r="C43">
-        <v>17.06807374840829</v>
+        <v>16.79424593350164</v>
       </c>
       <c r="D43">
-        <v>28.67107374840829</v>
+        <v>28.68024593350164</v>
       </c>
       <c r="E43">
-        <v>11.603</v>
+        <v>11.886</v>
       </c>
       <c r="F43">
-        <v>11.603</v>
+        <v>11.886</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4792,28 +4792,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M43">
-        <v>0.8342557000000002</v>
+        <v>0.8546034000000001</v>
       </c>
       <c r="N43">
-        <v>1.305744299999999</v>
+        <v>1.285396599999999</v>
       </c>
       <c r="O43">
-        <v>0.1958616449999998</v>
+        <v>0.1928094899999998</v>
       </c>
       <c r="P43">
-        <v>1.109882654999999</v>
+        <v>1.092587109999999</v>
       </c>
       <c r="Q43">
-        <v>10.069882655</v>
+        <v>10.05258711</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2956376945986725</v>
+        <v>0.2995390419506258</v>
       </c>
       <c r="T43">
-        <v>1.527976239189678</v>
+        <v>1.551836393936086</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.565160777445091</v>
+        <v>2.504085520839255</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4838,22 +4838,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.199400944331363</v>
+        <v>0.2007439488495091</v>
       </c>
       <c r="C44">
-        <v>16.79424593350164</v>
+        <v>16.362561669029</v>
       </c>
       <c r="D44">
-        <v>28.68024593350164</v>
+        <v>28.531561669029</v>
       </c>
       <c r="E44">
-        <v>11.886</v>
+        <v>12.169</v>
       </c>
       <c r="F44">
-        <v>11.886</v>
+        <v>12.169</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4874,45 +4874,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M44">
-        <v>0.8546034</v>
+        <v>0.9224102000000001</v>
       </c>
       <c r="N44">
-        <v>1.285396599999999</v>
+        <v>1.217589799999999</v>
       </c>
       <c r="O44">
-        <v>0.1928094899999998</v>
+        <v>0.1826384699999998</v>
       </c>
       <c r="P44">
-        <v>1.092587109999999</v>
+        <v>1.034951329999999</v>
       </c>
       <c r="Q44">
-        <v>10.05258711</v>
+        <v>9.994951329999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2995390419506258</v>
+        <v>0.3035772786833493</v>
       </c>
       <c r="T44">
-        <v>1.551836393936086</v>
+        <v>1.576533747094649</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.15</v>
       </c>
       <c r="W44">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.504085520839256</v>
+        <v>2.32000903719408</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4920,22 +4920,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2007439488495091</v>
+        <v>0.2006946533676553</v>
       </c>
       <c r="C45">
-        <v>16.362561669029</v>
+        <v>16.08499192088064</v>
       </c>
       <c r="D45">
-        <v>28.531561669029</v>
+        <v>28.53699192088064</v>
       </c>
       <c r="E45">
-        <v>12.169</v>
+        <v>12.452</v>
       </c>
       <c r="F45">
-        <v>12.169</v>
+        <v>12.452</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4956,28 +4956,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M45">
-        <v>0.9224102000000001</v>
+        <v>0.9438616000000001</v>
       </c>
       <c r="N45">
-        <v>1.217589799999999</v>
+        <v>1.196138399999999</v>
       </c>
       <c r="O45">
-        <v>0.1826384699999998</v>
+        <v>0.1794207599999998</v>
       </c>
       <c r="P45">
-        <v>1.034951329999999</v>
+        <v>1.016717639999999</v>
       </c>
       <c r="Q45">
-        <v>9.994951329999999</v>
+        <v>9.97671764</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3035772786833493</v>
+        <v>0.3077597381565272</v>
       </c>
       <c r="T45">
-        <v>1.576533747094649</v>
+        <v>1.602113148580303</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.32000903719408</v>
+        <v>2.267281559076033</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5002,22 +5002,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2006946533676553</v>
+        <v>0.2006453578858015</v>
       </c>
       <c r="C46">
-        <v>16.08499192088064</v>
+        <v>15.80742424014442</v>
       </c>
       <c r="D46">
-        <v>28.53699192088064</v>
+        <v>28.54242424014442</v>
       </c>
       <c r="E46">
-        <v>12.452</v>
+        <v>12.735</v>
       </c>
       <c r="F46">
-        <v>12.452</v>
+        <v>12.735</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5038,28 +5038,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M46">
-        <v>0.9438616000000001</v>
+        <v>0.9653130000000002</v>
       </c>
       <c r="N46">
-        <v>1.196138399999999</v>
+        <v>1.174686999999999</v>
       </c>
       <c r="O46">
-        <v>0.1794207599999998</v>
+        <v>0.1762030499999998</v>
       </c>
       <c r="P46">
-        <v>1.016717639999999</v>
+        <v>0.9984839499999989</v>
       </c>
       <c r="Q46">
-        <v>9.97671764</v>
+        <v>9.95848395</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3077597381565272</v>
+        <v>0.3120942870650935</v>
       </c>
       <c r="T46">
-        <v>1.602113148580303</v>
+        <v>1.628622710119981</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.267281559076033</v>
+        <v>2.216897524429898</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5084,22 +5084,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2006453578858015</v>
+        <v>0.2005960624039476</v>
       </c>
       <c r="C47">
-        <v>15.80742424014442</v>
+        <v>15.52985862800124</v>
       </c>
       <c r="D47">
-        <v>28.54242424014442</v>
+        <v>28.54785862800124</v>
       </c>
       <c r="E47">
-        <v>12.735</v>
+        <v>13.018</v>
       </c>
       <c r="F47">
-        <v>12.735</v>
+        <v>13.018</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5120,28 +5120,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M47">
-        <v>0.9653130000000002</v>
+        <v>0.9867644000000001</v>
       </c>
       <c r="N47">
-        <v>1.174686999999999</v>
+        <v>1.153235599999999</v>
       </c>
       <c r="O47">
-        <v>0.1762030499999998</v>
+        <v>0.1729853399999998</v>
       </c>
       <c r="P47">
-        <v>0.9984839499999989</v>
+        <v>0.9802502599999988</v>
       </c>
       <c r="Q47">
-        <v>9.95848395</v>
+        <v>9.940250259999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3120942870650935</v>
+        <v>0.3165893748221252</v>
       </c>
       <c r="T47">
-        <v>1.628622710119981</v>
+        <v>1.65611410727224</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.216897524429898</v>
+        <v>2.16870409998577</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5166,22 +5166,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2005960624039476</v>
+        <v>0.2005467669220938</v>
       </c>
       <c r="C48">
-        <v>15.52985862800124</v>
+        <v>15.25229508563285</v>
       </c>
       <c r="D48">
-        <v>28.54785862800124</v>
+        <v>28.55329508563285</v>
       </c>
       <c r="E48">
-        <v>13.018</v>
+        <v>13.301</v>
       </c>
       <c r="F48">
-        <v>13.018</v>
+        <v>13.301</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5202,28 +5202,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M48">
-        <v>0.9867644000000001</v>
+        <v>1.0082158</v>
       </c>
       <c r="N48">
-        <v>1.153235599999999</v>
+        <v>1.131784199999998</v>
       </c>
       <c r="O48">
-        <v>0.1729853399999998</v>
+        <v>0.1697676299999998</v>
       </c>
       <c r="P48">
-        <v>0.9802502599999988</v>
+        <v>0.9620165699999987</v>
       </c>
       <c r="Q48">
-        <v>9.940250259999999</v>
+        <v>9.92201657</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3165893748221252</v>
+        <v>0.3212540885322524</v>
       </c>
       <c r="T48">
-        <v>1.65611410727224</v>
+        <v>1.684642915637791</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.16870409998577</v>
+        <v>2.122561459560541</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5248,22 +5248,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2005467669220938</v>
+        <v>0.2004974714402399</v>
       </c>
       <c r="C49">
-        <v>15.25229508563285</v>
+        <v>14.97473361422197</v>
       </c>
       <c r="D49">
-        <v>28.55329508563285</v>
+        <v>28.55873361422197</v>
       </c>
       <c r="E49">
-        <v>13.301</v>
+        <v>13.584</v>
       </c>
       <c r="F49">
-        <v>13.301</v>
+        <v>13.584</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5284,28 +5284,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M49">
-        <v>1.0082158</v>
+        <v>1.0296672</v>
       </c>
       <c r="N49">
-        <v>1.131784199999998</v>
+        <v>1.110332799999999</v>
       </c>
       <c r="O49">
-        <v>0.1697676299999998</v>
+        <v>0.1665499199999998</v>
       </c>
       <c r="P49">
-        <v>0.9620165699999987</v>
+        <v>0.9437828799999988</v>
       </c>
       <c r="Q49">
-        <v>9.92201657</v>
+        <v>9.90378288</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3212540885322524</v>
+        <v>0.3260982143081537</v>
       </c>
       <c r="T49">
-        <v>1.684642915637791</v>
+        <v>1.714268985863556</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.122561459560541</v>
+        <v>2.07834142915303</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5330,22 +5330,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2004974714402399</v>
+        <v>0.2004481759583861</v>
       </c>
       <c r="C50">
-        <v>14.97473361422197</v>
+        <v>14.69717421495216</v>
       </c>
       <c r="D50">
-        <v>28.55873361422197</v>
+        <v>28.56417421495216</v>
       </c>
       <c r="E50">
-        <v>13.584</v>
+        <v>13.867</v>
       </c>
       <c r="F50">
-        <v>13.584</v>
+        <v>13.867</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5366,28 +5366,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M50">
-        <v>1.0296672</v>
+        <v>1.0511186</v>
       </c>
       <c r="N50">
-        <v>1.110332799999999</v>
+        <v>1.088881399999999</v>
       </c>
       <c r="O50">
-        <v>0.1665499199999998</v>
+        <v>0.1633322099999998</v>
       </c>
       <c r="P50">
-        <v>0.943782879999999</v>
+        <v>0.9255491899999989</v>
       </c>
       <c r="Q50">
-        <v>9.90378288</v>
+        <v>9.885549189999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3260982143081537</v>
+        <v>0.331132305800757</v>
       </c>
       <c r="T50">
-        <v>1.714268985863556</v>
+        <v>1.745056862764841</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.07834142915303</v>
+        <v>2.035926297945825</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5412,22 +5412,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2004481759583861</v>
+        <v>0.2064338804765323</v>
       </c>
       <c r="C51">
-        <v>14.69717421495216</v>
+        <v>13.76836236737701</v>
       </c>
       <c r="D51">
-        <v>28.56417421495216</v>
+        <v>27.91836236737701</v>
       </c>
       <c r="E51">
-        <v>13.867</v>
+        <v>14.15</v>
       </c>
       <c r="F51">
-        <v>13.867</v>
+        <v>14.15</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5448,45 +5448,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M51">
-        <v>1.0511186</v>
+        <v>1.2735</v>
       </c>
       <c r="N51">
-        <v>1.088881399999999</v>
+        <v>0.8664999999999987</v>
       </c>
       <c r="O51">
-        <v>0.1633322099999998</v>
+        <v>0.1299749999999998</v>
       </c>
       <c r="P51">
-        <v>0.9255491899999989</v>
+        <v>0.7365249999999989</v>
       </c>
       <c r="Q51">
-        <v>9.885549189999999</v>
+        <v>9.696524999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.331132305800757</v>
+        <v>0.3363677609530645</v>
       </c>
       <c r="T51">
-        <v>1.745056862764841</v>
+        <v>1.777076254742178</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.15</v>
       </c>
       <c r="W51">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.035926297945825</v>
+        <v>1.680408323517863</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5494,22 +5494,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2064338804765323</v>
+        <v>0.2065052849946784</v>
       </c>
       <c r="C52">
-        <v>13.76836236737701</v>
+        <v>13.47783457597624</v>
       </c>
       <c r="D52">
-        <v>27.91836236737701</v>
+        <v>27.91083457597624</v>
       </c>
       <c r="E52">
-        <v>14.15</v>
+        <v>14.433</v>
       </c>
       <c r="F52">
-        <v>14.15</v>
+        <v>14.433</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5530,28 +5530,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M52">
-        <v>1.2735</v>
+        <v>1.29897</v>
       </c>
       <c r="N52">
-        <v>0.8664999999999987</v>
+        <v>0.8410299999999988</v>
       </c>
       <c r="O52">
-        <v>0.1299749999999998</v>
+        <v>0.1261544999999998</v>
       </c>
       <c r="P52">
-        <v>0.7365249999999989</v>
+        <v>0.714875499999999</v>
       </c>
       <c r="Q52">
-        <v>9.696524999999999</v>
+        <v>9.674875500000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3363677609530645</v>
+        <v>0.341816908152405</v>
       </c>
       <c r="T52">
-        <v>1.777076254742178</v>
+        <v>1.810402560677773</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.680408323517863</v>
+        <v>1.647459140703788</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5576,22 +5576,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2065052849946784</v>
+        <v>0.2065766895128246</v>
       </c>
       <c r="C53">
-        <v>13.47783457597624</v>
+        <v>13.18731084300604</v>
       </c>
       <c r="D53">
-        <v>27.91083457597624</v>
+        <v>27.90331084300604</v>
       </c>
       <c r="E53">
-        <v>14.433</v>
+        <v>14.716</v>
       </c>
       <c r="F53">
-        <v>14.433</v>
+        <v>14.716</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5612,28 +5612,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M53">
-        <v>1.29897</v>
+        <v>1.32444</v>
       </c>
       <c r="N53">
-        <v>0.8410299999999988</v>
+        <v>0.8155599999999987</v>
       </c>
       <c r="O53">
-        <v>0.1261544999999998</v>
+        <v>0.1223339999999998</v>
       </c>
       <c r="P53">
-        <v>0.714875499999999</v>
+        <v>0.6932259999999989</v>
       </c>
       <c r="Q53">
-        <v>9.674875500000001</v>
+        <v>9.653226</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.341816908152405</v>
+        <v>0.3474931031517179</v>
       </c>
       <c r="T53">
-        <v>1.810402560677773</v>
+        <v>1.845117462694018</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.647459140703788</v>
+        <v>1.615777234151791</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5658,22 +5658,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2065766895128246</v>
+        <v>0.2066480940309708</v>
       </c>
       <c r="C54">
-        <v>13.18731084300604</v>
+        <v>12.8967911651853</v>
       </c>
       <c r="D54">
-        <v>27.90331084300604</v>
+        <v>27.8957911651853</v>
       </c>
       <c r="E54">
-        <v>14.716</v>
+        <v>14.999</v>
       </c>
       <c r="F54">
-        <v>14.716</v>
+        <v>14.999</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5694,28 +5694,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M54">
-        <v>1.32444</v>
+        <v>1.34991</v>
       </c>
       <c r="N54">
-        <v>0.8155599999999987</v>
+        <v>0.7900899999999988</v>
       </c>
       <c r="O54">
-        <v>0.1223339999999998</v>
+        <v>0.1185134999999998</v>
       </c>
       <c r="P54">
-        <v>0.6932259999999989</v>
+        <v>0.671576499999999</v>
       </c>
       <c r="Q54">
-        <v>9.653226</v>
+        <v>9.6315765</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3474931031517179</v>
+        <v>0.3534108383637676</v>
       </c>
       <c r="T54">
-        <v>1.845117462694018</v>
+        <v>1.881309594583294</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.615777234151791</v>
+        <v>1.585290871243267</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5740,22 +5740,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2066480940309708</v>
+        <v>0.2067194985491169</v>
       </c>
       <c r="C55">
-        <v>12.8967911651853</v>
+        <v>12.60627553923643</v>
       </c>
       <c r="D55">
-        <v>27.8957911651853</v>
+        <v>27.88827553923643</v>
       </c>
       <c r="E55">
-        <v>14.999</v>
+        <v>15.282</v>
       </c>
       <c r="F55">
-        <v>14.999</v>
+        <v>15.282</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5776,28 +5776,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M55">
-        <v>1.34991</v>
+        <v>1.37538</v>
       </c>
       <c r="N55">
-        <v>0.7900899999999988</v>
+        <v>0.7646199999999987</v>
       </c>
       <c r="O55">
-        <v>0.1185134999999998</v>
+        <v>0.1146929999999998</v>
       </c>
       <c r="P55">
-        <v>0.671576499999999</v>
+        <v>0.6499269999999989</v>
       </c>
       <c r="Q55">
-        <v>9.6315765</v>
+        <v>9.609926999999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3534108383637676</v>
+        <v>0.3595858664111237</v>
       </c>
       <c r="T55">
-        <v>1.881309594583294</v>
+        <v>1.919075297424279</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.585290871243267</v>
+        <v>1.55593363288691</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5822,22 +5822,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2067194985491169</v>
+        <v>0.2067909030672631</v>
       </c>
       <c r="C56">
-        <v>12.60627553923643</v>
+        <v>12.31576396188538</v>
       </c>
       <c r="D56">
-        <v>27.88827553923643</v>
+        <v>27.88076396188538</v>
       </c>
       <c r="E56">
-        <v>15.282</v>
+        <v>15.565</v>
       </c>
       <c r="F56">
-        <v>15.282</v>
+        <v>15.565</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5858,28 +5858,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M56">
-        <v>1.37538</v>
+        <v>1.40085</v>
       </c>
       <c r="N56">
-        <v>0.7646199999999987</v>
+        <v>0.7391499999999986</v>
       </c>
       <c r="O56">
-        <v>0.1146929999999998</v>
+        <v>0.1108724999999998</v>
       </c>
       <c r="P56">
-        <v>0.6499269999999989</v>
+        <v>0.6282774999999988</v>
       </c>
       <c r="Q56">
-        <v>9.609926999999999</v>
+        <v>9.5882775</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3595858664111237</v>
+        <v>0.3660353401494735</v>
       </c>
       <c r="T56">
-        <v>1.919075297424279</v>
+        <v>1.958519475947085</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.55593363288691</v>
+        <v>1.527643930470785</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5904,22 +5904,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2067909030672631</v>
+        <v>0.2068623075854092</v>
       </c>
       <c r="C57">
-        <v>12.31576396188538</v>
+        <v>12.0252564298616</v>
       </c>
       <c r="D57">
-        <v>27.88076396188538</v>
+        <v>27.8732564298616</v>
       </c>
       <c r="E57">
-        <v>15.565</v>
+        <v>15.848</v>
       </c>
       <c r="F57">
-        <v>15.565</v>
+        <v>15.848</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5940,28 +5940,28 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M57">
-        <v>1.40085</v>
+        <v>1.42632</v>
       </c>
       <c r="N57">
-        <v>0.7391499999999986</v>
+        <v>0.7136799999999985</v>
       </c>
       <c r="O57">
-        <v>0.1108724999999998</v>
+        <v>0.1070519999999998</v>
       </c>
       <c r="P57">
-        <v>0.6282774999999988</v>
+        <v>0.6066279999999987</v>
       </c>
       <c r="Q57">
-        <v>9.5882775</v>
+        <v>9.566628</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3660353401494735</v>
+        <v>0.372777971785021</v>
       </c>
       <c r="T57">
-        <v>1.958519475947085</v>
+        <v>1.999756571675473</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.527643930470785</v>
+        <v>1.50036457456952</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5986,22 +5986,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2068623075854092</v>
+        <v>0.2369551031599557</v>
       </c>
       <c r="C58">
-        <v>12.0252564298616</v>
+        <v>8.901502395095008</v>
       </c>
       <c r="D58">
-        <v>27.8732564298616</v>
+        <v>25.03250239509501</v>
       </c>
       <c r="E58">
-        <v>15.848</v>
+        <v>16.131</v>
       </c>
       <c r="F58">
-        <v>15.848</v>
+        <v>16.131</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6022,45 +6022,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M58">
-        <v>1.42632</v>
+        <v>2.368030800000001</v>
       </c>
       <c r="N58">
-        <v>0.7136799999999985</v>
+        <v>-0.2280308000000022</v>
       </c>
       <c r="O58">
-        <v>0.1070519999999998</v>
+        <v>-0.03420462000000033</v>
       </c>
       <c r="P58">
-        <v>0.6066279999999987</v>
+        <v>-0.1938261800000019</v>
       </c>
       <c r="Q58">
-        <v>9.566628</v>
+        <v>8.766173819999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.372777971785021</v>
+        <v>0.3828415333574449</v>
       </c>
       <c r="T58">
-        <v>1.999756571675473</v>
+        <v>2.061304061492759</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.15</v>
+        <v>0.1355556692928148</v>
       </c>
       <c r="W58">
-        <v>0.0765</v>
+        <v>0.1269004277478148</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.50036457456952</v>
+        <v>0.9037044619520987</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6068,22 +6068,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2369551031599557</v>
+        <v>0.2379651031599558</v>
       </c>
       <c r="C59">
-        <v>8.901502395095008</v>
+        <v>8.533167628290308</v>
       </c>
       <c r="D59">
-        <v>25.03250239509501</v>
+        <v>24.94716762829031</v>
       </c>
       <c r="E59">
-        <v>16.131</v>
+        <v>16.414</v>
       </c>
       <c r="F59">
-        <v>16.131</v>
+        <v>16.414</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6104,37 +6104,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M59">
-        <v>2.368030800000001</v>
+        <v>2.4095752</v>
       </c>
       <c r="N59">
-        <v>-0.2280308000000022</v>
+        <v>-0.2695752000000016</v>
       </c>
       <c r="O59">
-        <v>-0.03420462000000033</v>
+        <v>-0.04043628000000023</v>
       </c>
       <c r="P59">
-        <v>-0.1938261800000019</v>
+        <v>-0.2291389200000013</v>
       </c>
       <c r="Q59">
-        <v>8.766173819999999</v>
+        <v>8.73086108</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3828415333574449</v>
+        <v>0.3908663317707174</v>
       </c>
       <c r="T59">
-        <v>2.061304061492759</v>
+        <v>2.110382729623539</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1355556692928148</v>
+        <v>0.1332185025808698</v>
       </c>
       <c r="W59">
-        <v>0.1269004277478148</v>
+        <v>0.1272435238211283</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9037044619520987</v>
+        <v>0.8881233505391317</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6150,22 +6150,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2379651031599557</v>
+        <v>0.2389751031599557</v>
       </c>
       <c r="C60">
-        <v>8.533167628290315</v>
+        <v>8.165412690264549</v>
       </c>
       <c r="D60">
-        <v>24.94716762829031</v>
+        <v>24.86241269026455</v>
       </c>
       <c r="E60">
-        <v>16.414</v>
+        <v>16.697</v>
       </c>
       <c r="F60">
-        <v>16.414</v>
+        <v>16.697</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M60">
-        <v>2.4095752</v>
+        <v>2.4511196</v>
       </c>
       <c r="N60">
-        <v>-0.2695752000000011</v>
+        <v>-0.3111196000000014</v>
       </c>
       <c r="O60">
-        <v>-0.04043628000000016</v>
+        <v>-0.04666794000000021</v>
       </c>
       <c r="P60">
-        <v>-0.229138920000001</v>
+        <v>-0.2644516600000012</v>
       </c>
       <c r="Q60">
-        <v>8.73086108</v>
+        <v>8.69554834</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3908663317707173</v>
+        <v>0.399282583765125</v>
       </c>
       <c r="T60">
-        <v>2.110382729623538</v>
+        <v>2.161855479126551</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1332185025808698</v>
+        <v>0.1309605618591601</v>
       </c>
       <c r="W60">
-        <v>0.1272435238211283</v>
+        <v>0.1275749895190753</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8881233505391319</v>
+        <v>0.8730704123944008</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6232,22 +6232,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2389751031599557</v>
+        <v>0.2399851031599557</v>
       </c>
       <c r="C61">
-        <v>8.165412690264549</v>
+        <v>7.798231691336007</v>
       </c>
       <c r="D61">
-        <v>24.86241269026455</v>
+        <v>24.77823169133601</v>
       </c>
       <c r="E61">
-        <v>16.697</v>
+        <v>16.98</v>
       </c>
       <c r="F61">
-        <v>16.697</v>
+        <v>16.98</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6268,37 +6268,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M61">
-        <v>2.4511196</v>
+        <v>2.492664</v>
       </c>
       <c r="N61">
-        <v>-0.3111196000000014</v>
+        <v>-0.3526640000000016</v>
       </c>
       <c r="O61">
-        <v>-0.04666794000000021</v>
+        <v>-0.05289960000000025</v>
       </c>
       <c r="P61">
-        <v>-0.2644516600000012</v>
+        <v>-0.2997644000000014</v>
       </c>
       <c r="Q61">
-        <v>8.69554834</v>
+        <v>8.6602356</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.399282583765125</v>
+        <v>0.4081196483592532</v>
       </c>
       <c r="T61">
-        <v>2.161855479126551</v>
+        <v>2.215901866104715</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1309605618591601</v>
+        <v>0.1287778858281741</v>
       </c>
       <c r="W61">
-        <v>0.1275749895190753</v>
+        <v>0.1278954063604241</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8730704123944008</v>
+        <v>0.858519238854494</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6314,22 +6314,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2399851031599557</v>
+        <v>0.2409951031599557</v>
       </c>
       <c r="C62">
-        <v>7.798231691336007</v>
+        <v>7.43161882132069</v>
       </c>
       <c r="D62">
-        <v>24.77823169133601</v>
+        <v>24.69461882132069</v>
       </c>
       <c r="E62">
-        <v>16.98</v>
+        <v>17.263</v>
       </c>
       <c r="F62">
-        <v>16.98</v>
+        <v>17.263</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6350,37 +6350,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M62">
-        <v>2.492664</v>
+        <v>2.534208400000001</v>
       </c>
       <c r="N62">
-        <v>-0.3526640000000016</v>
+        <v>-0.3942084000000019</v>
       </c>
       <c r="O62">
-        <v>-0.05289960000000025</v>
+        <v>-0.05913126000000028</v>
       </c>
       <c r="P62">
-        <v>-0.2997644000000014</v>
+        <v>-0.3350771400000016</v>
       </c>
       <c r="Q62">
-        <v>8.6602356</v>
+        <v>8.62492286</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4081196483592532</v>
+        <v>0.4174098957530802</v>
       </c>
       <c r="T62">
-        <v>2.215901866104715</v>
+        <v>2.272719862671503</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1287778858281741</v>
+        <v>0.126666772945745</v>
       </c>
       <c r="W62">
-        <v>0.1278954063604241</v>
+        <v>0.1282053177315647</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.858519238854494</v>
+        <v>0.8444451529716334</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6396,22 +6396,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2409951031599557</v>
+        <v>0.2420051031599557</v>
       </c>
       <c r="C63">
-        <v>7.43161882132069</v>
+        <v>7.065568348195512</v>
       </c>
       <c r="D63">
-        <v>24.69461882132069</v>
+        <v>24.61156834819551</v>
       </c>
       <c r="E63">
-        <v>17.263</v>
+        <v>17.546</v>
       </c>
       <c r="F63">
-        <v>17.263</v>
+        <v>17.546</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6432,37 +6432,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M63">
-        <v>2.534208400000001</v>
+        <v>2.5757528</v>
       </c>
       <c r="N63">
-        <v>-0.3942084000000019</v>
+        <v>-0.4357528000000013</v>
       </c>
       <c r="O63">
-        <v>-0.05913126000000028</v>
+        <v>-0.06536292000000019</v>
       </c>
       <c r="P63">
-        <v>-0.3350771400000016</v>
+        <v>-0.3703898800000011</v>
       </c>
       <c r="Q63">
-        <v>8.62492286</v>
+        <v>8.58961012</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4174098957530802</v>
+        <v>0.427189103536056</v>
       </c>
       <c r="T63">
-        <v>2.272719862671503</v>
+        <v>2.332528280110227</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.126666772945745</v>
+        <v>0.1246237604788782</v>
       </c>
       <c r="W63">
-        <v>0.1282053177315647</v>
+        <v>0.1285052319617007</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8444451529716334</v>
+        <v>0.8308250698591879</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6478,22 +6478,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2420051031599557</v>
+        <v>0.2430151031599557</v>
       </c>
       <c r="C64">
-        <v>7.065568348195512</v>
+        <v>6.700074616788399</v>
       </c>
       <c r="D64">
-        <v>24.61156834819551</v>
+        <v>24.5290746167884</v>
       </c>
       <c r="E64">
-        <v>17.546</v>
+        <v>17.829</v>
       </c>
       <c r="F64">
-        <v>17.546</v>
+        <v>17.829</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6514,37 +6514,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M64">
-        <v>2.5757528</v>
+        <v>2.6172972</v>
       </c>
       <c r="N64">
-        <v>-0.4357528000000013</v>
+        <v>-0.4772972000000015</v>
       </c>
       <c r="O64">
-        <v>-0.06536292000000019</v>
+        <v>-0.07159458000000023</v>
       </c>
       <c r="P64">
-        <v>-0.3703898800000011</v>
+        <v>-0.4057026200000013</v>
       </c>
       <c r="Q64">
-        <v>8.58961012</v>
+        <v>8.55429738</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.427189103536056</v>
+        <v>0.4374969171451385</v>
       </c>
       <c r="T64">
-        <v>2.332528280110227</v>
+        <v>2.39556958497807</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1246237604788782</v>
+        <v>0.122645605550642</v>
       </c>
       <c r="W64">
-        <v>0.1285052319617007</v>
+        <v>0.1287956251051658</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8308250698591879</v>
+        <v>0.8176373703376134</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6560,22 +6560,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2430151031599557</v>
+        <v>0.2440251031599557</v>
       </c>
       <c r="C65">
-        <v>6.700074616788399</v>
+        <v>6.335132047494628</v>
       </c>
       <c r="D65">
-        <v>24.5290746167884</v>
+        <v>24.44713204749463</v>
       </c>
       <c r="E65">
-        <v>17.829</v>
+        <v>18.112</v>
       </c>
       <c r="F65">
-        <v>17.829</v>
+        <v>18.112</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6596,37 +6596,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M65">
-        <v>2.6172972</v>
+        <v>2.658841600000001</v>
       </c>
       <c r="N65">
-        <v>-0.4772972000000015</v>
+        <v>-0.5188416000000018</v>
       </c>
       <c r="O65">
-        <v>-0.07159458000000023</v>
+        <v>-0.07782624000000027</v>
       </c>
       <c r="P65">
-        <v>-0.4057026200000013</v>
+        <v>-0.4410153600000015</v>
       </c>
       <c r="Q65">
-        <v>8.55429738</v>
+        <v>8.518984639999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4374969171451385</v>
+        <v>0.4483773870658369</v>
       </c>
       <c r="T65">
-        <v>2.39556958497807</v>
+        <v>2.462113184560795</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.122645605550642</v>
+        <v>0.1207292679639132</v>
       </c>
       <c r="W65">
-        <v>0.1287956251051658</v>
+        <v>0.1290769434628976</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8176373703376134</v>
+        <v>0.8048617864260881</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6642,22 +6642,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2440251031599557</v>
+        <v>0.2833987134297676</v>
       </c>
       <c r="C66">
-        <v>6.335132047494628</v>
+        <v>3.235220421262113</v>
       </c>
       <c r="D66">
-        <v>24.44713204749463</v>
+        <v>21.63022042126211</v>
       </c>
       <c r="E66">
-        <v>18.112</v>
+        <v>18.395</v>
       </c>
       <c r="F66">
-        <v>18.112</v>
+        <v>18.395</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6678,45 +6678,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M66">
-        <v>2.658841600000001</v>
+        <v>3.693716</v>
       </c>
       <c r="N66">
-        <v>-0.5188416000000018</v>
+        <v>-1.553716000000001</v>
       </c>
       <c r="O66">
-        <v>-0.07782624000000027</v>
+        <v>-0.2330574000000002</v>
       </c>
       <c r="P66">
-        <v>-0.4410153600000015</v>
+        <v>-1.320658600000001</v>
       </c>
       <c r="Q66">
-        <v>8.518984639999999</v>
+        <v>7.639341399999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4483773870658369</v>
+        <v>0.469204198895752</v>
       </c>
       <c r="T66">
-        <v>2.462113184560795</v>
+        <v>2.589487373092688</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1207292679639132</v>
+        <v>0.08690435323127164</v>
       </c>
       <c r="W66">
-        <v>0.1290769434628976</v>
+        <v>0.1833496058711607</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8048617864260881</v>
+        <v>0.5793623548751443</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6724,22 +6724,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2833987134297676</v>
+        <v>0.2849487134297676</v>
       </c>
       <c r="C67">
-        <v>3.235220421262113</v>
+        <v>2.854549067006502</v>
       </c>
       <c r="D67">
-        <v>21.63022042126211</v>
+        <v>21.5325490670065</v>
       </c>
       <c r="E67">
-        <v>18.395</v>
+        <v>18.678</v>
       </c>
       <c r="F67">
-        <v>18.395</v>
+        <v>18.678</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6760,37 +6760,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M67">
-        <v>3.693716</v>
+        <v>3.7505424</v>
       </c>
       <c r="N67">
-        <v>-1.553716000000001</v>
+        <v>-1.610542400000002</v>
       </c>
       <c r="O67">
-        <v>-0.2330574000000002</v>
+        <v>-0.2415813600000002</v>
       </c>
       <c r="P67">
-        <v>-1.320658600000001</v>
+        <v>-1.368961040000001</v>
       </c>
       <c r="Q67">
-        <v>7.639341399999999</v>
+        <v>7.59103896</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.469204198895752</v>
+        <v>0.4816572635691564</v>
       </c>
       <c r="T67">
-        <v>2.589487373092688</v>
+        <v>2.665648766418943</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08690435323127164</v>
+        <v>0.08558762060655541</v>
       </c>
       <c r="W67">
-        <v>0.1833496058711607</v>
+        <v>0.1836140057822037</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5793623548751443</v>
+        <v>0.5705841373770361</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6806,22 +6806,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2849487134297676</v>
+        <v>0.2864987134297676</v>
       </c>
       <c r="C68">
-        <v>2.854549067006502</v>
+        <v>2.474755818509205</v>
       </c>
       <c r="D68">
-        <v>21.5325490670065</v>
+        <v>21.43575581850921</v>
       </c>
       <c r="E68">
-        <v>18.678</v>
+        <v>18.961</v>
       </c>
       <c r="F68">
-        <v>18.678</v>
+        <v>18.961</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6842,37 +6842,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M68">
-        <v>3.7505424</v>
+        <v>3.8073688</v>
       </c>
       <c r="N68">
-        <v>-1.610542400000002</v>
+        <v>-1.667368800000002</v>
       </c>
       <c r="O68">
-        <v>-0.2415813600000002</v>
+        <v>-0.2501053200000002</v>
       </c>
       <c r="P68">
-        <v>-1.368961040000001</v>
+        <v>-1.417263480000001</v>
       </c>
       <c r="Q68">
-        <v>7.59103896</v>
+        <v>7.54273652</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4816572635691564</v>
+        <v>0.4948650594348884</v>
       </c>
       <c r="T68">
-        <v>2.665648766418943</v>
+        <v>2.746426001764971</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08558762060655541</v>
+        <v>0.08431019343332324</v>
       </c>
       <c r="W68">
-        <v>0.1836140057822037</v>
+        <v>0.1838705131585887</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5705841373770361</v>
+        <v>0.5620679562221549</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6888,22 +6888,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2864987134297676</v>
+        <v>0.2880487134297676</v>
       </c>
       <c r="C69">
-        <v>2.474755818509205</v>
+        <v>2.09582888696395</v>
       </c>
       <c r="D69">
-        <v>21.43575581850921</v>
+        <v>21.33982888696395</v>
       </c>
       <c r="E69">
-        <v>18.961</v>
+        <v>19.244</v>
       </c>
       <c r="F69">
-        <v>18.961</v>
+        <v>19.244</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6924,37 +6924,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M69">
-        <v>3.8073688</v>
+        <v>3.864195200000001</v>
       </c>
       <c r="N69">
-        <v>-1.667368800000002</v>
+        <v>-1.724195200000002</v>
       </c>
       <c r="O69">
-        <v>-0.2501053200000002</v>
+        <v>-0.2586292800000002</v>
       </c>
       <c r="P69">
-        <v>-1.417263480000001</v>
+        <v>-1.465565920000002</v>
       </c>
       <c r="Q69">
-        <v>7.54273652</v>
+        <v>7.49443408</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4948650594348884</v>
+        <v>0.5088983425422288</v>
       </c>
       <c r="T69">
-        <v>2.746426001764971</v>
+        <v>2.832251814320128</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08431019343332324</v>
+        <v>0.08307033764753907</v>
       </c>
       <c r="W69">
-        <v>0.1838705131585887</v>
+        <v>0.1841194762003742</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5620679562221549</v>
+        <v>0.5538022509835938</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6970,22 +6970,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2880487134297676</v>
+        <v>0.2895987134297676</v>
       </c>
       <c r="C70">
-        <v>2.09582888696395</v>
+        <v>1.71775669364817</v>
       </c>
       <c r="D70">
-        <v>21.33982888696395</v>
+        <v>21.24475669364817</v>
       </c>
       <c r="E70">
-        <v>19.244</v>
+        <v>19.527</v>
       </c>
       <c r="F70">
-        <v>19.244</v>
+        <v>19.527</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7006,37 +7006,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M70">
-        <v>3.864195200000001</v>
+        <v>3.9210216</v>
       </c>
       <c r="N70">
-        <v>-1.724195200000002</v>
+        <v>-1.781021600000002</v>
       </c>
       <c r="O70">
-        <v>-0.2586292800000002</v>
+        <v>-0.2671532400000002</v>
       </c>
       <c r="P70">
-        <v>-1.465565920000002</v>
+        <v>-1.513868360000001</v>
       </c>
       <c r="Q70">
-        <v>7.49443408</v>
+        <v>7.446131639999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5088983425422288</v>
+        <v>0.5238369987532684</v>
       </c>
       <c r="T70">
-        <v>2.832251814320128</v>
+        <v>2.923614776072389</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08307033764753907</v>
+        <v>0.08186641971061821</v>
       </c>
       <c r="W70">
-        <v>0.1841194762003742</v>
+        <v>0.1843612229221079</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5538022509835938</v>
+        <v>0.5457761314041214</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7052,22 +7052,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2895987134297676</v>
+        <v>0.2911487134297676</v>
       </c>
       <c r="C71">
-        <v>1.71775669364817</v>
+        <v>1.340527865264004</v>
       </c>
       <c r="D71">
-        <v>21.24475669364817</v>
+        <v>21.15052786526401</v>
       </c>
       <c r="E71">
-        <v>19.527</v>
+        <v>19.81</v>
       </c>
       <c r="F71">
-        <v>19.527</v>
+        <v>19.81</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7088,37 +7088,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M71">
-        <v>3.9210216</v>
+        <v>3.977848000000001</v>
       </c>
       <c r="N71">
-        <v>-1.781021600000002</v>
+        <v>-1.837848000000002</v>
       </c>
       <c r="O71">
-        <v>-0.2671532400000002</v>
+        <v>-0.2756772000000003</v>
       </c>
       <c r="P71">
-        <v>-1.513868360000001</v>
+        <v>-1.562170800000002</v>
       </c>
       <c r="Q71">
-        <v>7.446131639999999</v>
+        <v>7.397829199999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5238369987532684</v>
+        <v>0.5397715653783773</v>
       </c>
       <c r="T71">
-        <v>2.923614776072389</v>
+        <v>3.021068601941469</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08186641971061821</v>
+        <v>0.08069689942903796</v>
       </c>
       <c r="W71">
-        <v>0.1843612229221079</v>
+        <v>0.1845960625946492</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5457761314041214</v>
+        <v>0.5379793295269197</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7134,22 +7134,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2911487134297676</v>
+        <v>0.2926987134297676</v>
       </c>
       <c r="C72">
-        <v>1.340527865264004</v>
+        <v>0.9641312294027173</v>
       </c>
       <c r="D72">
-        <v>21.15052786526401</v>
+        <v>21.05713122940272</v>
       </c>
       <c r="E72">
-        <v>19.81</v>
+        <v>20.093</v>
       </c>
       <c r="F72">
-        <v>19.81</v>
+        <v>20.093</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7170,37 +7170,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M72">
-        <v>3.977848000000001</v>
+        <v>4.034674400000001</v>
       </c>
       <c r="N72">
-        <v>-1.837848000000002</v>
+        <v>-1.894674400000002</v>
       </c>
       <c r="O72">
-        <v>-0.2756772000000003</v>
+        <v>-0.2842011600000003</v>
       </c>
       <c r="P72">
-        <v>-1.562170800000002</v>
+        <v>-1.610473240000002</v>
       </c>
       <c r="Q72">
-        <v>7.397829199999999</v>
+        <v>7.349526759999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5397715653783773</v>
+        <v>0.5568050676328042</v>
       </c>
       <c r="T72">
-        <v>3.021068601941469</v>
+        <v>3.125243381318762</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08069689942903796</v>
+        <v>0.07956032338074163</v>
       </c>
       <c r="W72">
-        <v>0.1845960625946492</v>
+        <v>0.1848242870651471</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5379793295269197</v>
+        <v>0.530402155871611</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7216,22 +7216,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2926987134297676</v>
+        <v>0.2942487134297675</v>
       </c>
       <c r="C73">
-        <v>0.9641312294027209</v>
+        <v>0.5885558101287742</v>
       </c>
       <c r="D73">
-        <v>21.05713122940272</v>
+        <v>20.96455581012878</v>
       </c>
       <c r="E73">
-        <v>20.093</v>
+        <v>20.376</v>
       </c>
       <c r="F73">
-        <v>20.093</v>
+        <v>20.376</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7252,37 +7252,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M73">
-        <v>4.0346744</v>
+        <v>4.0915008</v>
       </c>
       <c r="N73">
-        <v>-1.894674400000001</v>
+        <v>-1.951500800000002</v>
       </c>
       <c r="O73">
-        <v>-0.2842011600000002</v>
+        <v>-0.2927251200000002</v>
       </c>
       <c r="P73">
-        <v>-1.610473240000001</v>
+        <v>-1.658775680000001</v>
       </c>
       <c r="Q73">
-        <v>7.34952676</v>
+        <v>7.301224319999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.556805067632804</v>
+        <v>0.5750552486196898</v>
       </c>
       <c r="T73">
-        <v>3.12524338131876</v>
+        <v>3.236859216365859</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.07956032338074165</v>
+        <v>0.07845531888934247</v>
       </c>
       <c r="W73">
-        <v>0.1848242870651471</v>
+        <v>0.1850461719670201</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.530402155871611</v>
+        <v>0.523035459262283</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7298,22 +7298,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2942487134297675</v>
+        <v>0.2957987134297676</v>
       </c>
       <c r="C74">
-        <v>0.5885558101287742</v>
+        <v>0.2137908236798367</v>
       </c>
       <c r="D74">
-        <v>20.96455581012878</v>
+        <v>20.87279082367984</v>
       </c>
       <c r="E74">
-        <v>20.376</v>
+        <v>20.659</v>
       </c>
       <c r="F74">
-        <v>20.376</v>
+        <v>20.659</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7334,37 +7334,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M74">
-        <v>4.0915008</v>
+        <v>4.1483272</v>
       </c>
       <c r="N74">
-        <v>-1.951500800000002</v>
+        <v>-2.008327200000001</v>
       </c>
       <c r="O74">
-        <v>-0.2927251200000002</v>
+        <v>-0.3012490800000001</v>
       </c>
       <c r="P74">
-        <v>-1.658775680000001</v>
+        <v>-1.707078120000001</v>
       </c>
       <c r="Q74">
-        <v>7.301224319999999</v>
+        <v>7.25292188</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5750552486196898</v>
+        <v>0.5946572948648635</v>
       </c>
       <c r="T74">
-        <v>3.236859216365859</v>
+        <v>3.356742891046076</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07845531888934247</v>
+        <v>0.07738058849359805</v>
       </c>
       <c r="W74">
-        <v>0.1850461719670201</v>
+        <v>0.1852619778304855</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.523035459262283</v>
+        <v>0.5158705899573204</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7380,22 +7380,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2957987134297676</v>
+        <v>0.2973487134297676</v>
       </c>
       <c r="C75">
-        <v>0.2137908236798367</v>
+        <v>-0.1601743257207069</v>
       </c>
       <c r="D75">
-        <v>20.87279082367984</v>
+        <v>20.78182567427929</v>
       </c>
       <c r="E75">
-        <v>20.659</v>
+        <v>20.942</v>
       </c>
       <c r="F75">
-        <v>20.659</v>
+        <v>20.942</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7416,37 +7416,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M75">
-        <v>4.1483272</v>
+        <v>4.2051536</v>
       </c>
       <c r="N75">
-        <v>-2.008327200000001</v>
+        <v>-2.065153600000001</v>
       </c>
       <c r="O75">
-        <v>-0.3012490800000001</v>
+        <v>-0.3097730400000002</v>
       </c>
       <c r="P75">
-        <v>-1.707078120000001</v>
+        <v>-1.755380560000001</v>
       </c>
       <c r="Q75">
-        <v>7.25292188</v>
+        <v>7.20461944</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5946572948648635</v>
+        <v>0.6157671908212045</v>
       </c>
       <c r="T75">
-        <v>3.356742891046076</v>
+        <v>3.48584838685554</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.07738058849359805</v>
+        <v>0.07633490486530618</v>
       </c>
       <c r="W75">
-        <v>0.1852619778304855</v>
+        <v>0.1854719511030465</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5158705899573204</v>
+        <v>0.5088993657687079</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7462,22 +7462,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2973487134297676</v>
+        <v>0.2988987134297676</v>
       </c>
       <c r="C76">
-        <v>-0.1601743257207069</v>
+        <v>-0.5333500499422819</v>
       </c>
       <c r="D76">
-        <v>20.78182567427929</v>
+        <v>20.69164995005772</v>
       </c>
       <c r="E76">
-        <v>20.942</v>
+        <v>21.225</v>
       </c>
       <c r="F76">
-        <v>20.942</v>
+        <v>21.225</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7498,37 +7498,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M76">
-        <v>4.2051536</v>
+        <v>4.26198</v>
       </c>
       <c r="N76">
-        <v>-2.065153600000001</v>
+        <v>-2.121980000000002</v>
       </c>
       <c r="O76">
-        <v>-0.3097730400000002</v>
+        <v>-0.3182970000000002</v>
       </c>
       <c r="P76">
-        <v>-1.755380560000001</v>
+        <v>-1.803683000000001</v>
       </c>
       <c r="Q76">
-        <v>7.20461944</v>
+        <v>7.156317</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6157671908212045</v>
+        <v>0.6385658784540527</v>
       </c>
       <c r="T76">
-        <v>3.48584838685554</v>
+        <v>3.625282322329762</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07633490486530618</v>
+        <v>0.07531710613376877</v>
       </c>
       <c r="W76">
-        <v>0.1854719511030465</v>
+        <v>0.1856763250883393</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5088993657687079</v>
+        <v>0.5021140408917917</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7544,22 +7544,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2988987134297676</v>
+        <v>0.3283656195936772</v>
       </c>
       <c r="C77">
-        <v>-0.5333500499422819</v>
+        <v>-2.393160331126946</v>
       </c>
       <c r="D77">
-        <v>20.69164995005772</v>
+        <v>19.11483966887305</v>
       </c>
       <c r="E77">
-        <v>21.225</v>
+        <v>21.508</v>
       </c>
       <c r="F77">
-        <v>21.225</v>
+        <v>21.508</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7580,45 +7580,45 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M77">
-        <v>4.26198</v>
+        <v>5.0715864</v>
       </c>
       <c r="N77">
-        <v>-2.121980000000002</v>
+        <v>-2.931586400000001</v>
       </c>
       <c r="O77">
-        <v>-0.3182970000000002</v>
+        <v>-0.4397379600000002</v>
       </c>
       <c r="P77">
-        <v>-1.803683000000001</v>
+        <v>-2.491848440000001</v>
       </c>
       <c r="Q77">
-        <v>7.156317</v>
+        <v>6.46815156</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6385658784540527</v>
+        <v>0.6687515657392615</v>
       </c>
       <c r="T77">
-        <v>3.625282322329762</v>
+        <v>3.809894228109228</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07531710613376877</v>
+        <v>0.06329380487336266</v>
       </c>
       <c r="W77">
-        <v>0.1856763250883393</v>
+        <v>0.2208753208108611</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5021140408917917</v>
+        <v>0.4219586991557511</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7626,22 +7626,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3283656195936772</v>
+        <v>0.3302656195936772</v>
       </c>
       <c r="C78">
-        <v>-2.393160331126946</v>
+        <v>-2.769624532518929</v>
       </c>
       <c r="D78">
-        <v>19.11483966887305</v>
+        <v>19.02137546748107</v>
       </c>
       <c r="E78">
-        <v>21.508</v>
+        <v>21.791</v>
       </c>
       <c r="F78">
-        <v>21.508</v>
+        <v>21.791</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7662,37 +7662,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M78">
-        <v>5.0715864</v>
+        <v>5.1383178</v>
       </c>
       <c r="N78">
-        <v>-2.931586400000001</v>
+        <v>-2.998317800000001</v>
       </c>
       <c r="O78">
-        <v>-0.4397379600000002</v>
+        <v>-0.4497476700000002</v>
       </c>
       <c r="P78">
-        <v>-2.491848440000001</v>
+        <v>-2.548570130000001</v>
       </c>
       <c r="Q78">
-        <v>6.46815156</v>
+        <v>6.411429869999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6687515657392615</v>
+        <v>0.6958364164235773</v>
       </c>
       <c r="T78">
-        <v>3.809894228109228</v>
+        <v>3.975541803244412</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06329380487336266</v>
+        <v>0.06247180740747483</v>
       </c>
       <c r="W78">
-        <v>0.2208753208108611</v>
+        <v>0.2210691478133174</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4219586991557511</v>
+        <v>0.4164787160498322</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7708,22 +7708,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3302656195936772</v>
+        <v>0.3321656195936772</v>
       </c>
       <c r="C79">
-        <v>-2.769624532518929</v>
+        <v>-3.145179173441562</v>
       </c>
       <c r="D79">
-        <v>19.02137546748107</v>
+        <v>18.92882082655844</v>
       </c>
       <c r="E79">
-        <v>21.791</v>
+        <v>22.074</v>
       </c>
       <c r="F79">
-        <v>21.791</v>
+        <v>22.074</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7744,37 +7744,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M79">
-        <v>5.1383178</v>
+        <v>5.2050492</v>
       </c>
       <c r="N79">
-        <v>-2.998317800000001</v>
+        <v>-3.065049200000002</v>
       </c>
       <c r="O79">
-        <v>-0.4497476700000002</v>
+        <v>-0.4597573800000002</v>
       </c>
       <c r="P79">
-        <v>-2.548570130000001</v>
+        <v>-2.605291820000001</v>
       </c>
       <c r="Q79">
-        <v>6.411429869999999</v>
+        <v>6.354708179999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6958364164235773</v>
+        <v>0.7253835262610125</v>
       </c>
       <c r="T79">
-        <v>3.975541803244412</v>
+        <v>4.15624824884643</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06247180740747483</v>
+        <v>0.06167088679968669</v>
       </c>
       <c r="W79">
-        <v>0.2210691478133174</v>
+        <v>0.2212580048926339</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4164787160498322</v>
+        <v>0.4111392453312447</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7790,22 +7790,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3321656195936772</v>
+        <v>0.3340656195936772</v>
       </c>
       <c r="C80">
-        <v>-3.145179173441562</v>
+        <v>-3.519837466882777</v>
       </c>
       <c r="D80">
-        <v>18.92882082655844</v>
+        <v>18.83716253311723</v>
       </c>
       <c r="E80">
-        <v>22.074</v>
+        <v>22.357</v>
       </c>
       <c r="F80">
-        <v>22.074</v>
+        <v>22.357</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7826,37 +7826,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M80">
-        <v>5.2050492</v>
+        <v>5.2717806</v>
       </c>
       <c r="N80">
-        <v>-3.065049200000002</v>
+        <v>-3.131780600000002</v>
       </c>
       <c r="O80">
-        <v>-0.4597573800000002</v>
+        <v>-0.4697670900000002</v>
       </c>
       <c r="P80">
-        <v>-2.605291820000001</v>
+        <v>-2.662013510000001</v>
       </c>
       <c r="Q80">
-        <v>6.354708179999999</v>
+        <v>6.29798649</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7253835262610125</v>
+        <v>0.7577446465591562</v>
       </c>
       <c r="T80">
-        <v>4.15624824884643</v>
+        <v>4.354164832124833</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06167088679968669</v>
+        <v>0.06089024266298179</v>
       </c>
       <c r="W80">
-        <v>0.2212580048926339</v>
+        <v>0.2214420807800689</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4111392453312447</v>
+        <v>0.4059349510865453</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7872,22 +7872,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3340656195936772</v>
+        <v>0.3359656195936772</v>
       </c>
       <c r="C81">
-        <v>-3.519837466882777</v>
+        <v>-3.893612371140829</v>
       </c>
       <c r="D81">
-        <v>18.83716253311723</v>
+        <v>18.74638762885917</v>
       </c>
       <c r="E81">
-        <v>22.357</v>
+        <v>22.64</v>
       </c>
       <c r="F81">
-        <v>22.357</v>
+        <v>22.64</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7908,37 +7908,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M81">
-        <v>5.2717806</v>
+        <v>5.338512000000001</v>
       </c>
       <c r="N81">
-        <v>-3.131780600000002</v>
+        <v>-3.198512000000002</v>
       </c>
       <c r="O81">
-        <v>-0.4697670900000002</v>
+        <v>-0.4797768000000002</v>
       </c>
       <c r="P81">
-        <v>-2.662013510000001</v>
+        <v>-2.718735200000002</v>
       </c>
       <c r="Q81">
-        <v>6.29798649</v>
+        <v>6.2412648</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7577446465591562</v>
+        <v>0.7933418788871139</v>
       </c>
       <c r="T81">
-        <v>4.354164832124833</v>
+        <v>4.571873073731075</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06089024266298179</v>
+        <v>0.06012911462969452</v>
       </c>
       <c r="W81">
-        <v>0.2214420807800689</v>
+        <v>0.2216215547703181</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4059349510865453</v>
+        <v>0.4008607641979635</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7954,22 +7954,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3359656195936772</v>
+        <v>0.3378656195936772</v>
       </c>
       <c r="C82">
-        <v>-3.893612371140829</v>
+        <v>-4.266516595931531</v>
       </c>
       <c r="D82">
-        <v>18.74638762885917</v>
+        <v>18.65648340406847</v>
       </c>
       <c r="E82">
-        <v>22.64</v>
+        <v>22.923</v>
       </c>
       <c r="F82">
-        <v>22.64</v>
+        <v>22.923</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7990,37 +7990,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M82">
-        <v>5.338512000000001</v>
+        <v>5.405243400000001</v>
       </c>
       <c r="N82">
-        <v>-3.198512000000002</v>
+        <v>-3.265243400000002</v>
       </c>
       <c r="O82">
-        <v>-0.4797768000000002</v>
+        <v>-0.4897865100000003</v>
       </c>
       <c r="P82">
-        <v>-2.718735200000002</v>
+        <v>-2.775456890000002</v>
       </c>
       <c r="Q82">
-        <v>6.2412648</v>
+        <v>6.184543109999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.7933418788871139</v>
+        <v>0.8326861883022253</v>
       </c>
       <c r="T82">
-        <v>4.571873073731075</v>
+        <v>4.8124979723485</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06012911462969452</v>
+        <v>0.05938677988117978</v>
       </c>
       <c r="W82">
-        <v>0.2216215547703181</v>
+        <v>0.2217965973040178</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4008607641979635</v>
+        <v>0.3959118658745319</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8036,22 +8036,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3378656195936772</v>
+        <v>0.3397656195936772</v>
       </c>
       <c r="C83">
-        <v>-4.266516595931531</v>
+        <v>-4.638562608320552</v>
       </c>
       <c r="D83">
-        <v>18.65648340406847</v>
+        <v>18.56743739167945</v>
       </c>
       <c r="E83">
-        <v>22.923</v>
+        <v>23.206</v>
       </c>
       <c r="F83">
-        <v>22.923</v>
+        <v>23.206</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8072,37 +8072,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M83">
-        <v>5.405243400000001</v>
+        <v>5.471974800000001</v>
       </c>
       <c r="N83">
-        <v>-3.265243400000002</v>
+        <v>-3.331974800000002</v>
       </c>
       <c r="O83">
-        <v>-0.4897865100000003</v>
+        <v>-0.4997962200000003</v>
       </c>
       <c r="P83">
-        <v>-2.775456890000002</v>
+        <v>-2.832178580000002</v>
       </c>
       <c r="Q83">
-        <v>6.184543109999999</v>
+        <v>6.127821419999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8326861883022253</v>
+        <v>0.8764020876523488</v>
       </c>
       <c r="T83">
-        <v>4.8124979723485</v>
+        <v>5.079858970812305</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05938677988117978</v>
+        <v>0.05866255085823856</v>
       </c>
       <c r="W83">
-        <v>0.2217965973040178</v>
+        <v>0.2219673705076274</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3959118658745319</v>
+        <v>0.391083672388257</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8118,22 +8118,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3397656195936772</v>
+        <v>0.3416656195936772</v>
       </c>
       <c r="C84">
-        <v>-4.638562608320552</v>
+        <v>-5.009762638486695</v>
       </c>
       <c r="D84">
-        <v>18.56743739167945</v>
+        <v>18.47923736151331</v>
       </c>
       <c r="E84">
-        <v>23.206</v>
+        <v>23.489</v>
       </c>
       <c r="F84">
-        <v>23.206</v>
+        <v>23.489</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8154,37 +8154,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M84">
-        <v>5.471974800000001</v>
+        <v>5.538706200000001</v>
       </c>
       <c r="N84">
-        <v>-3.331974800000002</v>
+        <v>-3.398706200000002</v>
       </c>
       <c r="O84">
-        <v>-0.4997962200000003</v>
+        <v>-0.5098059300000003</v>
       </c>
       <c r="P84">
-        <v>-2.832178580000002</v>
+        <v>-2.888900270000002</v>
       </c>
       <c r="Q84">
-        <v>6.127821419999999</v>
+        <v>6.071099729999998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.8764020876523488</v>
+        <v>0.9252610339848401</v>
       </c>
       <c r="T84">
-        <v>5.079858970812305</v>
+        <v>5.3786742043895</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05866255085823856</v>
+        <v>0.05795577313705496</v>
       </c>
       <c r="W84">
-        <v>0.2219673705076274</v>
+        <v>0.2221340286942824</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.391083672388257</v>
+        <v>0.3863718209136997</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8200,22 +8200,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3416656195936772</v>
+        <v>0.3435656195936773</v>
       </c>
       <c r="C85">
-        <v>-5.009762638486695</v>
+        <v>-5.380128685321644</v>
       </c>
       <c r="D85">
-        <v>18.47923736151331</v>
+        <v>18.39187131467836</v>
       </c>
       <c r="E85">
-        <v>23.489</v>
+        <v>23.772</v>
       </c>
       <c r="F85">
-        <v>23.489</v>
+        <v>23.772</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8236,37 +8236,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M85">
-        <v>5.538706200000001</v>
+        <v>5.605437600000001</v>
       </c>
       <c r="N85">
-        <v>-3.398706200000002</v>
+        <v>-3.465437600000002</v>
       </c>
       <c r="O85">
-        <v>-0.5098059300000003</v>
+        <v>-0.5198156400000004</v>
       </c>
       <c r="P85">
-        <v>-2.888900270000002</v>
+        <v>-2.945621960000002</v>
       </c>
       <c r="Q85">
-        <v>6.071099729999998</v>
+        <v>6.014378039999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.9252610339848401</v>
+        <v>0.9802273486088927</v>
       </c>
       <c r="T85">
-        <v>5.3786742043895</v>
+        <v>5.714841342163845</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05795577313705496</v>
+        <v>0.05726582345685192</v>
       </c>
       <c r="W85">
-        <v>0.2221340286942824</v>
+        <v>0.2222967188288743</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3863718209136997</v>
+        <v>0.3817721563790129</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8282,22 +8282,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3435656195936772</v>
+        <v>0.3454656195936772</v>
       </c>
       <c r="C86">
-        <v>-5.380128685321637</v>
+        <v>-5.749672521871627</v>
       </c>
       <c r="D86">
-        <v>18.39187131467836</v>
+        <v>18.30532747812837</v>
       </c>
       <c r="E86">
-        <v>23.772</v>
+        <v>24.055</v>
       </c>
       <c r="F86">
-        <v>23.772</v>
+        <v>24.055</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8318,37 +8318,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M86">
-        <v>5.6054376</v>
+        <v>5.672169</v>
       </c>
       <c r="N86">
-        <v>-3.465437600000001</v>
+        <v>-3.532169000000001</v>
       </c>
       <c r="O86">
-        <v>-0.5198156400000001</v>
+        <v>-0.5298253500000002</v>
       </c>
       <c r="P86">
-        <v>-2.945621960000001</v>
+        <v>-3.002343650000001</v>
       </c>
       <c r="Q86">
-        <v>6.01437804</v>
+        <v>5.95765635</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.9802273486088919</v>
+        <v>1.042522505182818</v>
       </c>
       <c r="T86">
-        <v>5.71484134216384</v>
+        <v>6.095830764974764</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05726582345685193</v>
+        <v>0.05659210788677133</v>
       </c>
       <c r="W86">
-        <v>0.2222967188288743</v>
+        <v>0.2224555809602994</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3817721563790129</v>
+        <v>0.3772807192451422</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8364,22 +8364,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3454656195936772</v>
+        <v>0.3473656195936772</v>
       </c>
       <c r="C87">
-        <v>-5.749672521871627</v>
+        <v>-6.118405700626184</v>
       </c>
       <c r="D87">
-        <v>18.30532747812837</v>
+        <v>18.21959429937382</v>
       </c>
       <c r="E87">
-        <v>24.055</v>
+        <v>24.338</v>
       </c>
       <c r="F87">
-        <v>24.055</v>
+        <v>24.338</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8400,37 +8400,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M87">
-        <v>5.672169</v>
+        <v>5.7389004</v>
       </c>
       <c r="N87">
-        <v>-3.532169000000001</v>
+        <v>-3.598900400000002</v>
       </c>
       <c r="O87">
-        <v>-0.5298253500000002</v>
+        <v>-0.5398350600000003</v>
       </c>
       <c r="P87">
-        <v>-3.002343650000001</v>
+        <v>-3.059065340000001</v>
       </c>
       <c r="Q87">
-        <v>5.95765635</v>
+        <v>5.900934659999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.042522505182818</v>
+        <v>1.113716969838734</v>
       </c>
       <c r="T87">
-        <v>6.095830764974764</v>
+        <v>6.531247248187247</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05659210788677133</v>
+        <v>0.05593406012064607</v>
       </c>
       <c r="W87">
-        <v>0.2224555809602994</v>
+        <v>0.2226107486235517</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3772807192451422</v>
+        <v>0.3728937341376405</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8446,22 +8446,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3473656195936772</v>
+        <v>0.3492656195936772</v>
       </c>
       <c r="C88">
-        <v>-6.118405700626184</v>
+        <v>-6.486339558658951</v>
       </c>
       <c r="D88">
-        <v>18.21959429937382</v>
+        <v>18.13466044134105</v>
       </c>
       <c r="E88">
-        <v>24.338</v>
+        <v>24.621</v>
       </c>
       <c r="F88">
-        <v>24.338</v>
+        <v>24.621</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8482,37 +8482,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M88">
-        <v>5.7389004</v>
+        <v>5.8056318</v>
       </c>
       <c r="N88">
-        <v>-3.598900400000002</v>
+        <v>-3.665631800000002</v>
       </c>
       <c r="O88">
-        <v>-0.5398350600000003</v>
+        <v>-0.5498447700000002</v>
       </c>
       <c r="P88">
-        <v>-3.059065340000001</v>
+        <v>-3.115787030000002</v>
       </c>
       <c r="Q88">
-        <v>5.900934659999999</v>
+        <v>5.844212969999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.113716969838734</v>
+        <v>1.195864429057098</v>
       </c>
       <c r="T88">
-        <v>6.531247248187247</v>
+        <v>7.033650882663188</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05593406012064607</v>
+        <v>0.05529113988937428</v>
       </c>
       <c r="W88">
-        <v>0.2226107486235517</v>
+        <v>0.2227623492140856</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3728937341376405</v>
+        <v>0.3686075992624952</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8528,22 +8528,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3492656195936772</v>
+        <v>0.3511656195936772</v>
       </c>
       <c r="C89">
-        <v>-6.486339558658951</v>
+        <v>-6.853485222625384</v>
       </c>
       <c r="D89">
-        <v>18.13466044134105</v>
+        <v>18.05051477737462</v>
       </c>
       <c r="E89">
-        <v>24.621</v>
+        <v>24.904</v>
       </c>
       <c r="F89">
-        <v>24.621</v>
+        <v>24.904</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8564,37 +8564,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M89">
-        <v>5.8056318</v>
+        <v>5.872363200000001</v>
       </c>
       <c r="N89">
-        <v>-3.665631800000002</v>
+        <v>-3.732363200000002</v>
       </c>
       <c r="O89">
-        <v>-0.5498447700000002</v>
+        <v>-0.5598544800000003</v>
       </c>
       <c r="P89">
-        <v>-3.115787030000002</v>
+        <v>-3.172508720000002</v>
       </c>
       <c r="Q89">
-        <v>5.844212969999999</v>
+        <v>5.787491279999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.195864429057098</v>
+        <v>1.291703131478523</v>
       </c>
       <c r="T89">
-        <v>7.033650882663188</v>
+        <v>7.619788456218457</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05529113988937428</v>
+        <v>0.05466283148154048</v>
       </c>
       <c r="W89">
-        <v>0.2227623492140856</v>
+        <v>0.2229105043366528</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3686075992624952</v>
+        <v>0.3644188765436032</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8610,22 +8610,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3511656195936772</v>
+        <v>0.3530656195936772</v>
       </c>
       <c r="C90">
-        <v>-6.853485222625384</v>
+        <v>-7.219853613621964</v>
       </c>
       <c r="D90">
-        <v>18.05051477737462</v>
+        <v>17.96714638637804</v>
       </c>
       <c r="E90">
-        <v>24.904</v>
+        <v>25.187</v>
       </c>
       <c r="F90">
-        <v>24.904</v>
+        <v>25.187</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8646,37 +8646,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M90">
-        <v>5.872363200000001</v>
+        <v>5.939094600000001</v>
       </c>
       <c r="N90">
-        <v>-3.732363200000002</v>
+        <v>-3.799094600000002</v>
       </c>
       <c r="O90">
-        <v>-0.5598544800000003</v>
+        <v>-0.5698641900000002</v>
       </c>
       <c r="P90">
-        <v>-3.172508720000002</v>
+        <v>-3.229230410000002</v>
       </c>
       <c r="Q90">
-        <v>5.787491279999999</v>
+        <v>5.73076959</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.291703131478523</v>
+        <v>1.404967052522025</v>
       </c>
       <c r="T90">
-        <v>7.619788456218457</v>
+        <v>8.312496497692861</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05466283148154048</v>
+        <v>0.05404864236377036</v>
       </c>
       <c r="W90">
-        <v>0.2229105043366528</v>
+        <v>0.223055330130623</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3644188765436032</v>
+        <v>0.3603242824251357</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8692,22 +8692,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3530656195936772</v>
+        <v>0.3549656195936772</v>
       </c>
       <c r="C91">
-        <v>-7.219853613621964</v>
+        <v>-7.585455451911347</v>
       </c>
       <c r="D91">
-        <v>17.96714638637804</v>
+        <v>17.88454454808866</v>
       </c>
       <c r="E91">
-        <v>25.187</v>
+        <v>25.47</v>
       </c>
       <c r="F91">
-        <v>25.187</v>
+        <v>25.47</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8728,37 +8728,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M91">
-        <v>5.939094600000001</v>
+        <v>6.005826000000001</v>
       </c>
       <c r="N91">
-        <v>-3.799094600000002</v>
+        <v>-3.865826000000002</v>
       </c>
       <c r="O91">
-        <v>-0.5698641900000002</v>
+        <v>-0.5798739000000003</v>
       </c>
       <c r="P91">
-        <v>-3.229230410000002</v>
+        <v>-3.285952100000002</v>
       </c>
       <c r="Q91">
-        <v>5.73076959</v>
+        <v>5.6740479</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.404967052522025</v>
+        <v>1.540883757774228</v>
       </c>
       <c r="T91">
-        <v>8.312496497692861</v>
+        <v>9.143746147462149</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05404864236377036</v>
+        <v>0.0534481018930618</v>
       </c>
       <c r="W91">
-        <v>0.223055330130623</v>
+        <v>0.223196937573616</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3603242824251357</v>
+        <v>0.3563206792870787</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8774,22 +8774,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3549656195936772</v>
+        <v>0.3568656195936772</v>
       </c>
       <c r="C92">
-        <v>-7.585455451911347</v>
+        <v>-7.950301261517794</v>
       </c>
       <c r="D92">
-        <v>17.88454454808866</v>
+        <v>17.80269873848221</v>
       </c>
       <c r="E92">
-        <v>25.47</v>
+        <v>25.753</v>
       </c>
       <c r="F92">
-        <v>25.47</v>
+        <v>25.753</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8810,37 +8810,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M92">
-        <v>6.005826000000001</v>
+        <v>6.0725574</v>
       </c>
       <c r="N92">
-        <v>-3.865826000000002</v>
+        <v>-3.932557400000001</v>
       </c>
       <c r="O92">
-        <v>-0.5798739000000003</v>
+        <v>-0.5898836100000001</v>
       </c>
       <c r="P92">
-        <v>-3.285952100000002</v>
+        <v>-3.342673790000001</v>
       </c>
       <c r="Q92">
-        <v>5.6740479</v>
+        <v>5.61732621</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.540883757774228</v>
+        <v>1.707004175304698</v>
       </c>
       <c r="T92">
-        <v>9.143746147462149</v>
+        <v>10.15971794162461</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0534481018930618</v>
+        <v>0.05286076011401717</v>
       </c>
       <c r="W92">
-        <v>0.223196937573616</v>
+        <v>0.2233354327651147</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3563206792870787</v>
+        <v>0.3524050674267811</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8856,22 +8856,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3568656195936772</v>
+        <v>0.3587656195936772</v>
       </c>
       <c r="C93">
-        <v>-7.950301261517794</v>
+        <v>-8.314401374696992</v>
       </c>
       <c r="D93">
-        <v>17.80269873848221</v>
+        <v>17.72159862530301</v>
       </c>
       <c r="E93">
-        <v>25.753</v>
+        <v>26.036</v>
       </c>
       <c r="F93">
-        <v>25.753</v>
+        <v>26.036</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8892,37 +8892,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M93">
-        <v>6.0725574</v>
+        <v>6.139288800000001</v>
       </c>
       <c r="N93">
-        <v>-3.932557400000001</v>
+        <v>-3.999288800000002</v>
       </c>
       <c r="O93">
-        <v>-0.5898836100000001</v>
+        <v>-0.5998933200000003</v>
       </c>
       <c r="P93">
-        <v>-3.342673790000001</v>
+        <v>-3.399395480000002</v>
       </c>
       <c r="Q93">
-        <v>5.61732621</v>
+        <v>5.560604519999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.707004175304698</v>
+        <v>1.914654697217786</v>
       </c>
       <c r="T93">
-        <v>10.15971794162461</v>
+        <v>11.42968268432769</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05286076011401717</v>
+        <v>0.05228618663451697</v>
       </c>
       <c r="W93">
-        <v>0.2233354327651147</v>
+        <v>0.2234709171915809</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3524050674267811</v>
+        <v>0.3485745775634466</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8938,22 +8938,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3587656195936772</v>
+        <v>0.3606656195936772</v>
       </c>
       <c r="C94">
-        <v>-8.314401374696992</v>
+        <v>-8.677765936284253</v>
       </c>
       <c r="D94">
-        <v>17.72159862530301</v>
+        <v>17.64123406371575</v>
       </c>
       <c r="E94">
-        <v>26.036</v>
+        <v>26.319</v>
       </c>
       <c r="F94">
-        <v>26.036</v>
+        <v>26.319</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8974,37 +8974,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M94">
-        <v>6.139288800000001</v>
+        <v>6.206020200000001</v>
       </c>
       <c r="N94">
-        <v>-3.999288800000002</v>
+        <v>-4.066020200000002</v>
       </c>
       <c r="O94">
-        <v>-0.5998933200000003</v>
+        <v>-0.6099030300000003</v>
       </c>
       <c r="P94">
-        <v>-3.399395480000002</v>
+        <v>-3.456117170000002</v>
       </c>
       <c r="Q94">
-        <v>5.560604519999999</v>
+        <v>5.503882829999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.914654697217786</v>
+        <v>2.181633939677469</v>
       </c>
       <c r="T94">
-        <v>11.42968268432769</v>
+        <v>13.0624944963745</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05228618663451697</v>
+        <v>0.05172396957393077</v>
       </c>
       <c r="W94">
-        <v>0.2234709171915809</v>
+        <v>0.2236034879744671</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3485745775634466</v>
+        <v>0.3448264638262052</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9020,22 +9020,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3606656195936772</v>
+        <v>0.3625656195936772</v>
       </c>
       <c r="C95">
-        <v>-8.677765936284253</v>
+        <v>-9.040404907924906</v>
       </c>
       <c r="D95">
-        <v>17.64123406371575</v>
+        <v>17.5615950920751</v>
       </c>
       <c r="E95">
-        <v>26.319</v>
+        <v>26.602</v>
       </c>
       <c r="F95">
-        <v>26.319</v>
+        <v>26.602</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9056,37 +9056,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M95">
-        <v>6.206020200000001</v>
+        <v>6.272751600000001</v>
       </c>
       <c r="N95">
-        <v>-4.066020200000002</v>
+        <v>-4.132751600000002</v>
       </c>
       <c r="O95">
-        <v>-0.6099030300000003</v>
+        <v>-0.6199127400000003</v>
       </c>
       <c r="P95">
-        <v>-3.456117170000002</v>
+        <v>-3.512838860000002</v>
       </c>
       <c r="Q95">
-        <v>5.503882829999998</v>
+        <v>5.447161139999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.181633939677469</v>
+        <v>2.537606262957048</v>
       </c>
       <c r="T95">
-        <v>13.0624944963745</v>
+        <v>15.23957691243693</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05172396957393077</v>
+        <v>0.05117371457846342</v>
       </c>
       <c r="W95">
-        <v>0.2236034879744671</v>
+        <v>0.2237332381023983</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3448264638262052</v>
+        <v>0.3411580971897561</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9102,22 +9102,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3625656195936772</v>
+        <v>0.3644656195936772</v>
       </c>
       <c r="C96">
-        <v>-9.040404907924906</v>
+        <v>-9.402328072190681</v>
       </c>
       <c r="D96">
-        <v>17.5615950920751</v>
+        <v>17.48267192780932</v>
       </c>
       <c r="E96">
-        <v>26.602</v>
+        <v>26.885</v>
       </c>
       <c r="F96">
-        <v>26.602</v>
+        <v>26.885</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9138,37 +9138,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M96">
-        <v>6.272751600000001</v>
+        <v>6.339483</v>
       </c>
       <c r="N96">
-        <v>-4.132751600000002</v>
+        <v>-4.199483000000002</v>
       </c>
       <c r="O96">
-        <v>-0.6199127400000003</v>
+        <v>-0.6299224500000002</v>
       </c>
       <c r="P96">
-        <v>-3.512838860000002</v>
+        <v>-3.569560550000001</v>
       </c>
       <c r="Q96">
-        <v>5.447161139999999</v>
+        <v>5.39043945</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.537606262957048</v>
+        <v>3.035967515548459</v>
       </c>
       <c r="T96">
-        <v>15.23957691243693</v>
+        <v>18.28749229492432</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05117371457846342</v>
+        <v>0.05063504389869013</v>
       </c>
       <c r="W96">
-        <v>0.2237332381023983</v>
+        <v>0.2238602566486889</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3411580971897561</v>
+        <v>0.3375669593246009</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9184,22 +9184,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3644656195936772</v>
+        <v>0.3663656195936772</v>
       </c>
       <c r="C97">
-        <v>-9.402328072190681</v>
+        <v>-9.763545036585541</v>
       </c>
       <c r="D97">
-        <v>17.48267192780932</v>
+        <v>17.40445496341446</v>
       </c>
       <c r="E97">
-        <v>26.885</v>
+        <v>27.168</v>
       </c>
       <c r="F97">
-        <v>26.885</v>
+        <v>27.168</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9220,37 +9220,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M97">
-        <v>6.339483</v>
+        <v>6.406214400000001</v>
       </c>
       <c r="N97">
-        <v>-4.199483000000002</v>
+        <v>-4.266214400000002</v>
       </c>
       <c r="O97">
-        <v>-0.6299224500000002</v>
+        <v>-0.6399321600000002</v>
       </c>
       <c r="P97">
-        <v>-3.569560550000001</v>
+        <v>-3.626282240000001</v>
       </c>
       <c r="Q97">
-        <v>5.39043945</v>
+        <v>5.333717759999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.035967515548459</v>
+        <v>3.783509394435576</v>
       </c>
       <c r="T97">
-        <v>18.28749229492432</v>
+        <v>22.85936536865541</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05063504389869013</v>
+        <v>0.05010759552474544</v>
       </c>
       <c r="W97">
-        <v>0.2238602566486889</v>
+        <v>0.223984628975265</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3375669593246009</v>
+        <v>0.3340506368316363</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9266,22 +9266,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3663656195936772</v>
+        <v>0.3682656195936772</v>
       </c>
       <c r="C98">
-        <v>-9.763545036585537</v>
+        <v>-10.12406523744449</v>
       </c>
       <c r="D98">
-        <v>17.40445496341446</v>
+        <v>17.32693476255551</v>
       </c>
       <c r="E98">
-        <v>27.168</v>
+        <v>27.451</v>
       </c>
       <c r="F98">
-        <v>27.168</v>
+        <v>27.451</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9302,37 +9302,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M98">
-        <v>6.4062144</v>
+        <v>6.472945800000001</v>
       </c>
       <c r="N98">
-        <v>-4.266214400000001</v>
+        <v>-4.332945800000002</v>
       </c>
       <c r="O98">
-        <v>-0.6399321600000001</v>
+        <v>-0.6499418700000003</v>
       </c>
       <c r="P98">
-        <v>-3.626282240000001</v>
+        <v>-3.683003930000002</v>
       </c>
       <c r="Q98">
-        <v>5.33371776</v>
+        <v>5.276996069999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.783509394435566</v>
+        <v>5.029412525914088</v>
       </c>
       <c r="T98">
-        <v>22.85936536865535</v>
+        <v>30.4791538248738</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05010759552474545</v>
+        <v>0.0495910223750058</v>
       </c>
       <c r="W98">
-        <v>0.223984628975265</v>
+        <v>0.2241064369239736</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3340506368316363</v>
+        <v>0.3306068158333719</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9348,22 +9348,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3682656195936772</v>
+        <v>0.3701656195936772</v>
       </c>
       <c r="C99">
-        <v>-10.12406523744449</v>
+        <v>-10.48389794372863</v>
       </c>
       <c r="D99">
-        <v>17.32693476255551</v>
+        <v>17.25010205627137</v>
       </c>
       <c r="E99">
-        <v>27.451</v>
+        <v>27.734</v>
       </c>
       <c r="F99">
-        <v>27.451</v>
+        <v>27.734</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9384,37 +9384,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M99">
-        <v>6.472945800000001</v>
+        <v>6.539677200000001</v>
       </c>
       <c r="N99">
-        <v>-4.332945800000002</v>
+        <v>-4.399677200000002</v>
       </c>
       <c r="O99">
-        <v>-0.6499418700000003</v>
+        <v>-0.6599515800000003</v>
       </c>
       <c r="P99">
-        <v>-3.683003930000002</v>
+        <v>-3.739725620000002</v>
       </c>
       <c r="Q99">
-        <v>5.276996069999999</v>
+        <v>5.220274379999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.029412525914088</v>
+        <v>7.521218788871133</v>
       </c>
       <c r="T99">
-        <v>30.4791538248738</v>
+        <v>45.7187307373107</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0495910223750058</v>
+        <v>0.0490849915344445</v>
       </c>
       <c r="W99">
-        <v>0.2241064369239736</v>
+        <v>0.224225758996178</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3306068158333719</v>
+        <v>0.3272332768962968</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9430,22 +9430,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3701656195936772</v>
+        <v>0.3720656195936772</v>
       </c>
       <c r="C100">
-        <v>-10.48389794372863</v>
+        <v>-10.84305226071971</v>
       </c>
       <c r="D100">
-        <v>17.25010205627137</v>
+        <v>17.17394773928029</v>
       </c>
       <c r="E100">
-        <v>27.734</v>
+        <v>28.017</v>
       </c>
       <c r="F100">
-        <v>27.734</v>
+        <v>28.017</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9466,37 +9466,37 @@
         <v>2.139999999999999</v>
       </c>
       <c r="M100">
-        <v>6.539677200000001</v>
+        <v>6.6064086</v>
       </c>
       <c r="N100">
-        <v>-4.399677200000002</v>
+        <v>-4.466408600000001</v>
       </c>
       <c r="O100">
-        <v>-0.6599515800000003</v>
+        <v>-0.6699612900000002</v>
       </c>
       <c r="P100">
-        <v>-3.739725620000002</v>
+        <v>-3.796447310000001</v>
       </c>
       <c r="Q100">
-        <v>5.220274379999999</v>
+        <v>5.16355269</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.521218788871133</v>
+        <v>14.99663757774227</v>
       </c>
       <c r="T100">
-        <v>45.7187307373107</v>
+        <v>91.4374614746214</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0490849915344445</v>
+        <v>0.04858918353914709</v>
       </c>
       <c r="W100">
-        <v>0.224225758996178</v>
+        <v>0.2243426705214691</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9504,91 +9504,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3272332768962968</v>
+        <v>0.3239278902609807</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3720656195936772</v>
-      </c>
-      <c r="C101">
-        <v>-10.84305226071971</v>
-      </c>
-      <c r="D101">
-        <v>17.17394773928029</v>
-      </c>
-      <c r="E101">
-        <v>28.017</v>
-      </c>
-      <c r="F101">
-        <v>28.017</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>28.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.1</v>
-      </c>
-      <c r="K101">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="L101">
-        <v>2.139999999999999</v>
-      </c>
-      <c r="M101">
-        <v>6.6064086</v>
-      </c>
-      <c r="N101">
-        <v>-4.466408600000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.6699612900000002</v>
-      </c>
-      <c r="P101">
-        <v>-3.796447310000001</v>
-      </c>
-      <c r="Q101">
-        <v>5.16355269</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>14.99663757774227</v>
-      </c>
-      <c r="T101">
-        <v>91.4374614746214</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04858918353914709</v>
-      </c>
-      <c r="W101">
-        <v>0.2243426705214691</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3239278902609807</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
